--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Brouillons à éditer" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$251</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 12 — tes dix corrections</t>
+          <t>Version 13 — deux jours avant la diffusion</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -472,198 +472,162 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Le média kit</t>
+          <t>Ce que les envois ont appris</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>« Notre média kit est ici » annonçait un envoi que personne n'avait demandé. Ta formule remet la décision au journaliste et ouvre la porte au collègue qui prendra peut-être le sujet : « Si ça vous intéresse de couvrir (ou un.e collègue?)… ». Dans les 238 brouillons.</t>
+          <t>Trois réponses sur tes 23, et une seule entrevue décrochée : Guillaume Roy, en vingt-six minutes. C'est le seul courriel dont l'objet nommait sa région, et le seul qui lui donnait quelqu'un à aller voir — Sabin Tremblay et ses champs. Tout le détail est dans 11-ce-que-les-envois-ont-appris.md.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>L'ordre</t>
+          <t>Objets régionalisés</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Plus une seule allusion à la diffusion avant qu'elle soit annoncée. « Cette année, la date tombe presque au même endroit » et « la diffusion tombe cinq ans jour pour jour après votre article » sautent : une coïncidence de calendrier ne passe pas devant la nouvelle.</t>
+          <t>Les 38 contacts de la Mauricie, du Centre-du-Québec, de l'Estrie, de la Montérégie et du Lac-Saint-Jean reçoivent « L'asclépiade de [leur région] à Dragons' Den! ». Les autres suivent les formes courtes que tu avais réécrites à la main.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Les remerciements</t>
+          <t>Ce jeudi</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Les 16 remerciements sont raccourcis et collés au paragraphe du rappel. Plus de compliment sur un choix éditorial — « merci d'avoir ouvert le cahier climatique à une plante » se lit comme une lecture de dossier. Un fait ne reste que s'il dit ce que l'article a donné : « le texte a beaucoup circulé chez nos clients ».</t>
+          <t>« Le 17 septembre prochain » est devenu « Ce jeudi 17 septembre » : à deux jours, la date n'est plus une information, c'est un délai. La disponibilité ne promet plus « la semaine du 14 septembre », qui est cette semaine.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Les missions</t>
+          <t>Presse anglophone</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>« Depuis, tout mon temps va à mes 2 grandes missions » parlait de ton emploi du temps. « On se concentre sur nos 2 grandes missions » parle de l'entreprise, comme dans ta correction à Fanny Samson.</t>
+          <t>L'angle H avait zéro contact pour une émission de CBC. Neuf adresses, toutes publiées par le média lui-même sur sa page de contact — CBC Media Centre, Global National et Global Montréal, le Report on Business, Retail Insider, FashionUnited, et trois revues textiles dont Innovation in Textiles, qui a couvert l'asclépiade de Vegeto en février. Onglet « Presse anglophone ».</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Tes dix textes</t>
+          <t>Adresses non devinées</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Larocque, Bérubé, Pouliot, Paquet, Anne-Sophie Roy, Lafrance, Marie Tison, Simard, Samson et Lemieux sont les tiens, mot pour mot. Seule la ligne du média kit y est uniformisée, là où tu ne l'avais pas encore changée.</t>
+          <t>Beaucoup de rédactions anglophones ne publient qu'un formulaire. Je ne comble pas le trou avec des « prénom.nom@ » déduits : une adresse inventée rebondit et abîme le domaine qui doit livrer l'infolettre de prévente.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Registre</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Melissa Paquet, Anne-Sophie Roy et Annie Lafrance passent au « tu », comme tes textes. Avec Bérubé et Pouliot, ça fait cinq.</t>
-        </is>
-      </c>
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Sorties</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Sylvie Lacombe, Justine Friis et Francis Higgins ne sont plus dans ton chiffrier : je les ai retirés. Dis-le si c'était un accident et je les remets. Rhéane Portelance et Anaïs Elboujdaini et Ariane Aubert Bonn sortent aussi, sur ta demande.</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>À mettre à jour</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Jean-Michel Leprince</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Promu de la liste froide à la liste chaude. Son adresse reste à confirmer : elle vient d'une recherche web, pas d'un échange.</t>
-        </is>
-      </c>
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Valérie Simard</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ne couvre plus la mode, elle est aux actualités environnement et climat. Elle a transmis à Olivia Lévy, à La Presse, et veut être tenue au courant des RÉPERCUSSIONS du passage, pas de l'annonce.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Ce qui reste à vérifier</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sylvie Lemieux</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>N'est plus au Journal de Montréal : Les Affaires et La Terre de chez nous. Elle dit elle-même que le volet agricole intéresserait La Terre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="2" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Anne-Sophie Roy</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>En congé de maternité. Tu as écrit à Mme Courteau à sa place.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Ne pas envoyer</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Anne-Sophie Roy à l'adresse Québecor, doublon de sa ligne Radio-Canada.</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Six salutations</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Fiches FPJQ mal formées, signalées dans la colonne Précaution.</t>
-        </is>
-      </c>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Rappels</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Faits nouveaux</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Tes corrections ajoutent deux choses que je n'avais pas : les soins pour la peau à l'huile de graines d'asclépiade, et « mitaines » plutôt que « moufles ». Les deux sont corrigés là où tu les as écrits, mais pas ailleurs — dis-moi si le catalogue doit être revu partout.</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Diffusion</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Rappels</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Envoi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Missive, un appel par journaliste, suivi des ouvertures et des clics désactivé. Le mode par défaut dépose un brouillon.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Diffusion</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Prévente le samedi 12 septembre à 9 h.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Envoi</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Missive depuis media@lasclay.com, un appel par journaliste, suivi des ouvertures et des clics désactivé, environ 60 par jour. Le mode par défaut dépose un brouillon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Interdits CBC</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Rien sur l'issue avant le 17. Aucun logo ni « vu à Dragons' Den ».</t>
         </is>
@@ -680,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N242"/>
+  <dimension ref="A1:N251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -752,7 +716,7 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Brouillon v12</t>
+          <t>Brouillon v13</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
@@ -2262,7 +2226,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2271,7 +2235,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Il y a une belle histoire de sciences dans l'asclépiade. La soie attachée à ses graines n'est pas un poil : c'est un tube creux enduit d'une cire hydrophobe, et les fibres portent une charge qui les fait se repousser. C'est ce qui forme le parachute autour de la graine, et c'est ce qui emprisonne l'air. Chaque follicule en produit plus de 200.
 On en fait de l'isolant pour des manteaux et des mitaines. Et c'est la seule plante que les chenilles du monarque peuvent manger, ce qui est toute la raison d'être de l'entreprise.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vos lecteurs aimeraient voir comment une gousse devient un manteau.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2331,7 +2295,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2340,7 +2304,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2400,7 +2364,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2409,7 +2373,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2469,7 +2433,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2478,7 +2442,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2538,7 +2502,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2547,7 +2511,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2607,7 +2571,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2616,7 +2580,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2676,7 +2640,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2685,7 +2649,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2745,7 +2709,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2754,7 +2718,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2814,7 +2778,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2823,7 +2787,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -2883,7 +2847,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2892,9 +2856,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -2952,7 +2916,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2961,7 +2925,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3021,7 +2985,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3030,7 +2994,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3090,7 +3054,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3099,7 +3063,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3159,7 +3123,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3168,7 +3132,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3228,7 +3192,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3237,7 +3201,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3297,7 +3261,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3306,7 +3270,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3366,7 +3330,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3375,7 +3339,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3435,7 +3399,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3444,7 +3408,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3504,7 +3468,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Mauricie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3512,7 +3476,7 @@
           <t>Bonjour Gabriel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 L'asclépiade a été une histoire mauricienne avant d'être la nôtre : l'usine de Saint-Tite achetait 90 % des récoltes du Québec. On a démarré après la chute de cette filière, et six ans plus tard on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet : huit ans après Saint-Tite, il reste quelque chose de cette promesse-là, et ça se raconte.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3572,7 +3536,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3581,7 +3545,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3641,7 +3605,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3650,7 +3614,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3710,7 +3674,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3719,9 +3683,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -3779,7 +3743,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3788,7 +3752,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3848,7 +3812,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3857,7 +3821,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -3917,7 +3881,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3926,9 +3890,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -3986,7 +3950,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3995,7 +3959,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4055,7 +4019,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4064,7 +4028,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4124,7 +4088,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4133,9 +4097,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -4193,7 +4157,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4202,7 +4166,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4262,7 +4226,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4271,7 +4235,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4331,7 +4295,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4340,7 +4304,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4400,7 +4364,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4409,9 +4373,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -4469,7 +4433,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4478,7 +4442,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4538,7 +4502,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4547,7 +4511,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4607,7 +4571,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4616,7 +4580,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4676,7 +4640,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4685,9 +4649,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -4745,7 +4709,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4754,7 +4718,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4814,7 +4778,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4823,9 +4787,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -4883,7 +4847,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4892,7 +4856,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -4952,7 +4916,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4961,7 +4925,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5021,7 +4985,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5030,7 +4994,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5090,7 +5054,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5099,7 +5063,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5159,7 +5123,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5168,7 +5132,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5228,7 +5192,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Mauricie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5237,7 +5201,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment industriel au Québec. L'usine achetait 90 % des récoltes de la province avant que la filière se casse en 2018.
 On a démarré après. Six ans plus tard, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part parce que vos lecteurs ont vu la promesse de l'asclépiade de plus près que n'importe qui. Qui sait, peut-être vous inspirer un sujet sur ce que la plante est devenue depuis. Je peux parler des volumes, de la récolte, et de ce qui reste à régler.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5297,7 +5261,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5306,7 +5270,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5366,7 +5330,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5375,7 +5339,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5435,7 +5399,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5444,7 +5408,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5504,7 +5468,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5513,9 +5477,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -5573,7 +5537,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5582,7 +5546,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5642,7 +5606,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5651,7 +5615,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5711,7 +5675,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -5720,7 +5684,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5780,7 +5744,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5789,9 +5753,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -5849,7 +5813,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -5858,7 +5822,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5918,7 +5882,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -5927,7 +5891,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -5987,7 +5951,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5996,7 +5960,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6056,7 +6020,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6065,7 +6029,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6125,7 +6089,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6134,7 +6098,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6194,7 +6158,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6203,7 +6167,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6263,7 +6227,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6272,7 +6236,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6332,7 +6296,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6341,7 +6305,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6401,7 +6365,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6410,7 +6374,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6470,7 +6434,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6479,7 +6443,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6539,7 +6503,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6548,7 +6512,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6608,7 +6572,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6617,7 +6581,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6677,7 +6641,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -6686,7 +6650,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6746,7 +6710,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -6755,7 +6719,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6815,7 +6779,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -6824,7 +6788,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -6884,7 +6848,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -6893,9 +6857,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -6953,7 +6917,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -6962,7 +6926,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7022,7 +6986,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7031,7 +6995,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7091,7 +7055,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7100,7 +7064,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7160,7 +7124,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7169,7 +7133,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7229,7 +7193,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7238,7 +7202,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7298,7 +7262,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7307,7 +7271,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7367,7 +7331,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7376,7 +7340,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7436,7 +7400,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7445,7 +7409,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7505,7 +7469,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7514,7 +7478,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7574,7 +7538,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -7583,9 +7547,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -7643,7 +7607,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -7652,9 +7616,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -7712,7 +7676,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -7721,7 +7685,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7781,7 +7745,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -7790,7 +7754,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7850,7 +7814,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -7859,7 +7823,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7919,7 +7883,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -7928,7 +7892,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -7988,7 +7952,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -7997,7 +7961,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8057,7 +8021,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8066,7 +8030,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8126,7 +8090,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8135,7 +8099,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8195,7 +8159,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8204,7 +8168,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8264,7 +8228,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8273,7 +8237,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8333,7 +8297,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8342,7 +8306,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8402,7 +8366,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8411,7 +8375,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8471,7 +8435,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8480,7 +8444,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8540,7 +8504,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -8549,7 +8513,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8609,7 +8573,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -8618,7 +8582,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8678,7 +8642,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -8687,7 +8651,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8747,7 +8711,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -8756,7 +8720,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8816,7 +8780,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -8825,7 +8789,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -8885,7 +8849,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -8894,9 +8858,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -8954,7 +8918,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Mauricie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -8963,7 +8927,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9023,7 +8987,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9032,7 +8996,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9092,7 +9056,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9101,7 +9065,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9161,7 +9125,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9170,7 +9134,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9230,7 +9194,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9239,7 +9203,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9299,7 +9263,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Mauricie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9308,7 +9272,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9368,7 +9332,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9377,7 +9341,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9437,7 +9401,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9446,7 +9410,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9506,7 +9470,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -9515,7 +9479,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9575,7 +9539,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -9584,7 +9548,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9644,7 +9608,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -9653,7 +9617,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9713,7 +9677,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -9722,9 +9686,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -9782,7 +9746,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -9791,7 +9755,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9851,7 +9815,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -9860,7 +9824,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9920,7 +9884,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -9929,7 +9893,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -9989,7 +9953,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -9998,7 +9962,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10058,7 +10022,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10067,7 +10031,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10127,7 +10091,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade du Centre-du-Québec à Dragons' Den!</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10136,9 +10100,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -10196,7 +10160,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10205,7 +10169,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10265,7 +10229,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10274,7 +10238,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10334,7 +10298,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10343,7 +10307,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10403,7 +10367,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -10412,7 +10376,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10472,7 +10436,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -10481,7 +10445,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10541,7 +10505,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -10550,7 +10514,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10610,7 +10574,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade du Centre-du-Québec à Dragons' Den!</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -10619,7 +10583,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10679,7 +10643,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -10688,7 +10652,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10748,7 +10712,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -10757,7 +10721,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10817,7 +10781,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -10826,7 +10790,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10886,7 +10850,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Mauricie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -10895,7 +10859,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -10955,7 +10919,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -10964,7 +10928,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11024,7 +10988,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11033,7 +10997,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11093,7 +11057,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade du Centre-du-Québec à Dragons' Den!</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11102,7 +11066,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11162,7 +11126,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11171,7 +11135,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11231,7 +11195,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11240,9 +11204,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -11300,7 +11264,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11309,7 +11273,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11369,7 +11333,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -11378,7 +11342,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11438,7 +11402,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -11447,7 +11411,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11507,7 +11471,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -11516,7 +11480,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11576,7 +11540,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -11585,9 +11549,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -11645,7 +11609,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -11654,9 +11618,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -11714,7 +11678,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -11723,7 +11687,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11783,7 +11747,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -11792,7 +11756,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11852,7 +11816,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -11861,7 +11825,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -11921,7 +11885,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -11930,9 +11894,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -11990,7 +11954,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -11999,9 +11963,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -12059,7 +12023,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12068,9 +12032,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -12128,7 +12092,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12137,7 +12101,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12197,7 +12161,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12206,7 +12170,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12266,7 +12230,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -12275,7 +12239,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12335,7 +12299,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -12344,7 +12308,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12404,7 +12368,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -12413,7 +12377,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12473,7 +12437,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -12482,7 +12446,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12542,7 +12506,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -12551,7 +12515,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12611,7 +12575,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -12620,7 +12584,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12680,7 +12644,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de l'Estrie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -12689,7 +12653,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12749,7 +12713,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -12758,7 +12722,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12818,7 +12782,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -12827,7 +12791,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12887,7 +12851,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -12896,7 +12860,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -12956,7 +12920,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -12965,9 +12929,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -13025,7 +12989,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -13034,7 +12998,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13094,7 +13058,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -13103,7 +13067,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13163,7 +13127,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -13172,7 +13136,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13232,7 +13196,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -13241,9 +13205,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -13301,7 +13265,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -13310,7 +13274,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13370,7 +13334,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -13379,7 +13343,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13439,7 +13403,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -13448,7 +13412,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13508,7 +13472,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -13517,7 +13481,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13577,7 +13541,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -13586,7 +13550,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13702,7 +13666,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -13711,7 +13675,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13771,7 +13735,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -13780,7 +13744,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13840,7 +13804,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -13849,7 +13813,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -13909,7 +13873,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -13918,9 +13882,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -13978,7 +13942,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -13987,9 +13951,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -14103,7 +14067,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -14112,7 +14076,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14172,7 +14136,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -14181,7 +14145,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14241,7 +14205,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -14250,7 +14214,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14310,7 +14274,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -14319,9 +14283,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -14379,7 +14343,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -14388,7 +14352,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14448,7 +14412,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -14457,7 +14421,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14517,7 +14481,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -14526,7 +14490,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14586,7 +14550,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -14595,7 +14559,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14655,7 +14619,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -14664,9 +14628,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -14724,7 +14688,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -14733,9 +14697,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -14793,7 +14757,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -14802,7 +14766,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14862,7 +14826,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -14871,7 +14835,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -14931,7 +14895,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade du Centre-du-Québec à Dragons' Den!</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -14940,7 +14904,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15000,7 +14964,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -15009,7 +14973,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15069,7 +15033,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -15078,9 +15042,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -15138,7 +15102,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -15147,7 +15111,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15207,7 +15171,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade du Centre-du-Québec à Dragons' Den!</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -15216,7 +15180,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15276,7 +15240,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -15285,7 +15249,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15345,7 +15309,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -15354,9 +15318,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -15414,7 +15378,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -15423,7 +15387,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15483,7 +15447,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -15492,9 +15456,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -15552,7 +15516,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -15561,7 +15525,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15621,7 +15585,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -15630,7 +15594,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15690,7 +15654,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -15699,7 +15663,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15759,7 +15723,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -15768,7 +15732,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15828,7 +15792,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K223" s="2" t="inlineStr">
@@ -15837,9 +15801,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -15897,7 +15861,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade du Centre-du-Québec à Dragons' Den!</t>
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -15906,7 +15870,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -15966,7 +15930,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -15975,7 +15939,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16035,7 +15999,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -16044,7 +16008,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16104,7 +16068,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K227" s="2" t="inlineStr">
@@ -16113,7 +16077,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16173,7 +16137,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -16182,7 +16146,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16242,7 +16206,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
@@ -16251,7 +16215,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16311,7 +16275,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -16320,9 +16284,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -16380,7 +16344,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Montérégie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -16389,7 +16353,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16449,7 +16413,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -16458,7 +16422,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16518,7 +16482,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -16527,7 +16491,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16587,7 +16551,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -16596,9 +16560,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -16656,7 +16620,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -16665,7 +16629,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16725,7 +16689,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -16734,9 +16698,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -16794,7 +16758,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade de la Mauricie à Dragons' Den!</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -16803,7 +16767,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -16863,7 +16827,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -16872,9 +16836,9 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -16932,7 +16896,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr">
@@ -16941,7 +16905,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -17001,7 +16965,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -17010,7 +16974,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -17070,7 +17034,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -17079,7 +17043,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -17139,7 +17103,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade et les monarques à Dragons' Den!</t>
         </is>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -17148,7 +17112,7 @@
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -17160,13 +17124,670 @@
       <c r="M242" s="5" t="n"/>
       <c r="N242" s="6" t="n"/>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CBC Media Centre</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>CBC Media Centre</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>cbcpr@cbc.ca</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>cbc.ca/mediacentre/contact</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>I'm writing to the people who handle publicity for the show: we're the Quebec company in episode 1, and we have high-resolution images and a founder available all week if that is useful to anyone covering the season premiere.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+I'm writing to the people who handle publicity for the show: we're the Quebec company in episode 1, and we have high-resolution images and a founder available all week if that is useful to anyone covering the season premiere.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L243" s="5" t="n"/>
+      <c r="M243" s="5" t="n"/>
+      <c r="N243" s="6" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Innovation in Textiles</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Innovation in Textiles</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>editor@innovationintextiles.com</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>innovationintextiles.com/contact</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments — which makes us, as far as we know, the only ones doing the whole chain.</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments — which makes us, as far as we know, the only ones doing the whole chain.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L244" s="5" t="n"/>
+      <c r="M244" s="5" t="n"/>
+      <c r="N244" s="6" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Textile World</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Textile World</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>jborneman@textileworld.com</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>textileworld.com/contact</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments, which is the part nobody had managed to hold.</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments, which is the part nobody had managed to hold.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L245" s="5" t="n"/>
+      <c r="M245" s="5" t="n"/>
+      <c r="N245" s="6" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Retail Insider</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Retail Insider</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>insider@retail-insider.com</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>retail-insider.com/contact-us</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L246" s="5" t="n"/>
+      <c r="M246" s="5" t="n"/>
+      <c r="N246" s="6" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>FashionUnited Canada</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>FashionUnited Canada</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>news@fashionunited.com</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>fashionunited.ca/contact</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Plant-based insulation is one of the few places where outerwear can actually leave animal and petroleum fibres behind, and milkweed is the rare one that also feeds a threatened pollinator.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Plant-based insulation is one of the few places where outerwear can actually leave animal and petroleum fibres behind, and milkweed is the rare one that also feeds a threatened pollinator.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L247" s="5" t="n"/>
+      <c r="M247" s="5" t="n"/>
+      <c r="N247" s="6" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>The Globe and Mail — Report on Business</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>The Globe and Mail — Report on Business</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ROB@globeandmail.com</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>theglobeandmail.com/about/contact</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L248" s="5" t="n"/>
+      <c r="M248" s="5" t="n"/>
+      <c r="N248" s="6" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Global National</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Global National</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>globalnational@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>globalnews.ca/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L249" s="5" t="n"/>
+      <c r="M249" s="5" t="n"/>
+      <c r="N249" s="6" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Global News — news tips</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Global News — news tips</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>newstips@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>globalnews.ca/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L250" s="5" t="n"/>
+      <c r="M250" s="5" t="n"/>
+      <c r="N250" s="6" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Global Montreal</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Global Montreal</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>montreal@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>globalnews.ca/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — the national broadcast on Thursday is a local story first.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — the national broadcast on Thursday is a local story first.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L251" s="5" t="n"/>
+      <c r="M251" s="5" t="n"/>
+      <c r="N251" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N242"/>
+  <autoFilter ref="A1:N251"/>
   <dataValidations count="2">
-    <dataValidation sqref="N2:N242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"à réécrire au complet,à corriger,bon,ne pas envoyer"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"tu,vous,—"</formula1>
     </dataValidation>
   </dataValidations>

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Brouillons à éditer" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$275</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N251"/>
+  <dimension ref="A1:N275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17132,17 +17132,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CBC Media Centre</t>
+          <t>The Canadian Press</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>CBC Media Centre</t>
+          <t>The Canadian Press</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>cbcpr@cbc.ca</t>
+          <t>newsroom@thecanadianpress.com</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>cbc.ca/mediacentre/contact</t>
+          <t>Fil de presse national</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>I'm writing to the people who handle publicity for the show: we're the Quebec company in episode 1, and we have high-resolution images and a founder available all week if that is useful to anyone covering the season premiere.</t>
+          <t>I'm writing to the wire first because if this is worth two paragraphs, it's worth them in every paper in the country: a Quebec company insulating winter coats with the only plant monarch caterpillars can eat is going on national television Thursday.</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -17180,7 +17180,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-I'm writing to the people who handle publicity for the show: we're the Quebec company in episode 1, and we have high-resolution images and a founder available all week if that is useful to anyone covering the season premiere.
+I'm writing to the wire first because if this is worth two paragraphs, it's worth them in every paper in the country: a Quebec company insulating winter coats with the only plant monarch caterpillars can eat is going on national television Thursday.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
@@ -17205,50 +17205,488 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
+          <t>BNN Bloomberg</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>BNN Bloomberg</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>bnnassignmentdesk@bellmedia.ca</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Pupitre des affectations</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>The business story: we built our own processing because no subcontractor would touch the fibre, changed our manufacturing model last year to survive, and are now pitching on national television.</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+The business story: we built our own processing because no subcontractor would touch the fibre, changed our manufacturing model last year to survive, and are now pitching on national television.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L244" s="5" t="n"/>
+      <c r="M244" s="5" t="n"/>
+      <c r="N244" s="6" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ROB@globeandmail.com</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Report on Business</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L245" s="5" t="n"/>
+      <c r="M245" s="5" t="n"/>
+      <c r="N245" s="6" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Global National</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Global National</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>globalnational@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Pupitre national</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L246" s="5" t="n"/>
+      <c r="M246" s="5" t="n"/>
+      <c r="N246" s="6" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Global News</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Global News</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>newstips@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Ligne de nouvelles</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L247" s="5" t="n"/>
+      <c r="M247" s="5" t="n"/>
+      <c r="N247" s="6" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Global Montreal</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Global Montreal</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>montreal@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Pupitre de Montréal</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — Thursday's national broadcast is a local story first.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — Thursday's national broadcast is a local story first.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L248" s="5" t="n"/>
+      <c r="M248" s="5" t="n"/>
+      <c r="N248" s="6" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Retail Insider</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Retail Insider</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>insider@retail-insider.com</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L249" s="5" t="n"/>
+      <c r="M249" s="5" t="n"/>
+      <c r="N249" s="6" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
           <t>Innovation in Textiles</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>Innovation in Textiles</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>editor@innovationintextiles.com</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>innovationintextiles.com/contact</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
         <is>
           <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments — which makes us, as far as we know, the only ones doing the whole chain.</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
+      <c r="H250" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J244" s="2" t="inlineStr">
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
         <is>
           <t>Quebec milkweed on Dragons' Den — this Thursday</t>
         </is>
       </c>
-      <c r="K244" s="2" t="inlineStr">
+      <c r="K250" s="2" t="inlineStr">
         <is>
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
@@ -17266,62 +17704,135 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L244" s="5" t="n"/>
-      <c r="M244" s="5" t="n"/>
-      <c r="N244" s="6" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="L250" s="5" t="n"/>
+      <c r="M250" s="5" t="n"/>
+      <c r="N250" s="6" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>anglo</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Knitting Industry</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Knitting Industry</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>editor@knittingindustry.com</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L251" s="5" t="n"/>
+      <c r="M251" s="5" t="n"/>
+      <c r="N251" s="6" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
         <is>
           <t>Textile World</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>Textile World</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>jborneman@textileworld.com</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>textileworld.com/contact</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Rédaction technique</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
         <is>
           <t>Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments, which is the part nobody had managed to hold.</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
+      <c r="H252" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J245" s="2" t="inlineStr">
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
         <is>
           <t>Quebec milkweed on Dragons' Den — this Thursday</t>
         </is>
       </c>
-      <c r="K245" s="2" t="inlineStr">
+      <c r="K252" s="2" t="inlineStr">
         <is>
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
@@ -17339,135 +17850,62 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L245" s="5" t="n"/>
-      <c r="M245" s="5" t="n"/>
-      <c r="N245" s="6" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="L252" s="5" t="n"/>
+      <c r="M252" s="5" t="n"/>
+      <c r="N252" s="6" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>anglo</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Retail Insider</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Retail Insider</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>insider@retail-insider.com</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>FashionUnited Canada</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>FashionUnited Canada</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>news@fashionunited.com</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>retail-insider.com/contact-us</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr">
-        <is>
-          <t>We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Plant-based insulation is one of the few places where outerwear can actually leave animal and petroleum fibres behind, and milkweed is the rare one that also feeds a threatened pollinator.</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J246" s="2" t="inlineStr">
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
         <is>
           <t>Quebec milkweed on Dragons' Den — this Thursday</t>
         </is>
       </c>
-      <c r="K246" s="2" t="inlineStr">
-        <is>
-          <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
-Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.
-This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
-Happy to answer any questions, and available for an interview this week.
-Warmly,
-__
-Gabriel Gouveia
-Co-founder
-+1 (581) 982-5857
-Lasclay.com</t>
-        </is>
-      </c>
-      <c r="L246" s="5" t="n"/>
-      <c r="M246" s="5" t="n"/>
-      <c r="N246" s="6" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>anglo</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>FashionUnited Canada</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>FashionUnited Canada</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>news@fashionunited.com</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>fashionunited.ca/contact</t>
-        </is>
-      </c>
-      <c r="G247" s="2" t="inlineStr">
-        <is>
-          <t>Plant-based insulation is one of the few places where outerwear can actually leave animal and petroleum fibres behind, and milkweed is the rare one that also feeds a threatened pollinator.</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J247" s="2" t="inlineStr">
-        <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
-        </is>
-      </c>
-      <c r="K247" s="2" t="inlineStr">
+      <c r="K253" s="2" t="inlineStr">
         <is>
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
@@ -17485,67 +17923,67 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L247" s="5" t="n"/>
-      <c r="M247" s="5" t="n"/>
-      <c r="N247" s="6" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="L253" s="5" t="n"/>
+      <c r="M253" s="5" t="n"/>
+      <c r="N253" s="6" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>anglo</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>The Globe and Mail — Report on Business</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>The Globe and Mail — Report on Business</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>ROB@globeandmail.com</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Better Farming</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Better Farming</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>editor@betterfarming.com</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>theglobeandmail.com/about/contact</t>
-        </is>
-      </c>
-      <c r="G248" s="2" t="inlineStr">
-        <is>
-          <t>A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest — that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J248" s="2" t="inlineStr">
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
         <is>
           <t>Quebec milkweed on Dragons' Den — this Thursday</t>
         </is>
       </c>
-      <c r="K248" s="2" t="inlineStr">
+      <c r="K254" s="2" t="inlineStr">
         <is>
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.
+The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest — that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
@@ -17558,236 +17996,1466 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L248" s="5" t="n"/>
-      <c r="M248" s="5" t="n"/>
-      <c r="N248" s="6" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>anglo</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Global National</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Global National</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>globalnational@globalnews.ca</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>globalnews.ca/pages/contact-us</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J249" s="2" t="inlineStr">
-        <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
-        </is>
-      </c>
-      <c r="K249" s="2" t="inlineStr">
-        <is>
-          <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
-Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.
-This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
-Happy to answer any questions, and available for an interview this week.
-Warmly,
+      <c r="L254" s="5" t="n"/>
+      <c r="M254" s="5" t="n"/>
+      <c r="N254" s="6" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Johanne Lapierre</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>johanne.j.lapierre@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Rédactrice en chef</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Johanne,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
 __
 Gabriel Gouveia
-Co-founder
+Co-fondateur
 +1 (581) 982-5857
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L249" s="5" t="n"/>
-      <c r="M249" s="5" t="n"/>
-      <c r="N249" s="6" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>anglo</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Global News — news tips</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Global News — news tips</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>newstips@globalnews.ca</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>globalnews.ca/pages/contact-us</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J250" s="2" t="inlineStr">
-        <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
-        </is>
-      </c>
-      <c r="K250" s="2" t="inlineStr">
-        <is>
-          <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
-Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and the same plant is the only thing monarch caterpillars eat.
-This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
-Happy to answer any questions, and available for an interview this week.
-Warmly,
+      <c r="L255" s="5" t="n"/>
+      <c r="M255" s="5" t="n"/>
+      <c r="N255" s="6" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Catherine Mercier</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>catherine.mercier@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Animatrice</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Catherine,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
 __
 Gabriel Gouveia
-Co-founder
+Co-fondateur
 +1 (581) 982-5857
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L250" s="5" t="n"/>
-      <c r="M250" s="5" t="n"/>
-      <c r="N250" s="6" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>anglo</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Global Montreal</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Global Montreal</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>montreal@globalnews.ca</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>globalnews.ca/pages/contact-us</t>
-        </is>
-      </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — the national broadcast on Thursday is a local story first.</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J251" s="2" t="inlineStr">
-        <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
-        </is>
-      </c>
-      <c r="K251" s="2" t="inlineStr">
-        <is>
-          <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
-Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — the national broadcast on Thursday is a local story first.
-This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
-Happy to answer any questions, and available for an interview this week.
-Warmly,
+      <c r="L256" s="5" t="n"/>
+      <c r="M256" s="5" t="n"/>
+      <c r="N256" s="6" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>France Beaudoin</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>france.beaudoin@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Journaliste</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour France,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
 __
 Gabriel Gouveia
-Co-founder
+Co-fondateur
 +1 (581) 982-5857
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L251" s="5" t="n"/>
-      <c r="M251" s="5" t="n"/>
-      <c r="N251" s="6" t="n"/>
+      <c r="L257" s="5" t="n"/>
+      <c r="M257" s="5" t="n"/>
+      <c r="N257" s="6" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Gilbert Bégin</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>gilbert.begin@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Journaliste</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Gilbert,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L258" s="5" t="n"/>
+      <c r="M258" s="5" t="n"/>
+      <c r="N258" s="6" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Carine Monat</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>carine.monat@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Journaliste</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Carine,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L259" s="5" t="n"/>
+      <c r="M259" s="5" t="n"/>
+      <c r="N259" s="6" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Maxime Poiré</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>maxime.poire@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Journaliste</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Maxime,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L260" s="5" t="n"/>
+      <c r="M260" s="5" t="n"/>
+      <c r="N260" s="6" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Marie Maude Pontbriand</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>marie-maude.pontbriand@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Journaliste</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Marie,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L261" s="5" t="n"/>
+      <c r="M261" s="5" t="n"/>
+      <c r="N261" s="6" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Julie Vaillancourt</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>julie.vaillancourt@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Journaliste</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Julie,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L262" s="5" t="n"/>
+      <c r="M262" s="5" t="n"/>
+      <c r="N262" s="6" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Marc-Yvan Hébert</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>marc-yvan.hebert@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Journaliste-réalisateur</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Marc-Yvan,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L263" s="5" t="n"/>
+      <c r="M263" s="5" t="n"/>
+      <c r="N263" s="6" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Benoit Livernoche</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>La Semaine verte (Radio-Canada)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>benoit.livernoche@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Journaliste-réalisateur</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour Benoit,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L264" s="5" t="n"/>
+      <c r="M264" s="5" t="n"/>
+      <c r="N264" s="6" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>TVA Nouvelles</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>TVA Nouvelles</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>nouvelles@tva.ca</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Pupitre national</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L265" s="5" t="n"/>
+      <c r="M265" s="5" t="n"/>
+      <c r="N265" s="6" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>TVA Québec</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>TVA Québec</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>nouvelles.quebec@tva.ca</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Pupitre de Québec</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Notre atelier est à Québec, et c'est là que la soie d'asclépiade devient de l'isolant.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L266" s="5" t="n"/>
+      <c r="M266" s="5" t="n"/>
+      <c r="N266" s="6" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TVA Saguenay</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TVA Saguenay</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>nouvelles.cjpm@tva.ca</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Pupitre du Saguenay</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Notre fournisseur du Lac-Saint-Jean, Sabin Tremblay de L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L267" s="5" t="n"/>
+      <c r="M267" s="5" t="n"/>
+      <c r="N267" s="6" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>TVA Trois-Rivières</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TVA Trois-Rivières</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>nouvelles.chem@tva.ca</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Pupitre de la Mauricie</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="n"/>
+      <c r="M268" s="5" t="n"/>
+      <c r="N268" s="6" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>TVA Sherbrooke</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>TVA Sherbrooke</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>nouvelles.sherbrooke@tva.ca</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Pupitre de l'Estrie</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Une des premières usines de transformation de la fibre était à Granby, et l'Estrie compte encore des producteurs d'asclépiade.
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L269" s="5" t="n"/>
+      <c r="M269" s="5" t="n"/>
+      <c r="N269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>TVA Est-du-Québec</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TVA Est-du-Québec</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>nouvelles.cfer@tva.ca</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Pupitre de l'Est-du-Québec</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="n"/>
+      <c r="M270" s="5" t="n"/>
+      <c r="N270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Québecor Québec</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Québecor Québec</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>quebec@quebecormedia.com</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Salle de nouvelles</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L271" s="5" t="n"/>
+      <c r="M271" s="5" t="n"/>
+      <c r="N271" s="6" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Québecor Montréal</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Québecor Montréal</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>montreal@quebecormedia.com</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Salle de nouvelles</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L272" s="5" t="n"/>
+      <c r="M272" s="5" t="n"/>
+      <c r="N272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Québecor Sherbrooke</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Québecor Sherbrooke</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>sherbrooke@quebecormedia.com</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Salle de nouvelles</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L273" s="5" t="n"/>
+      <c r="M273" s="5" t="n"/>
+      <c r="N273" s="6" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Québecor Trois-Rivières</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Québecor Trois-Rivières</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>trois-rivieres@quebecormedia.com</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Salle de nouvelles</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L274" s="5" t="n"/>
+      <c r="M274" s="5" t="n"/>
+      <c r="N274" s="6" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ajout</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Québecor Est-du-Québec</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Québecor Est-du-Québec</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>estquebec@quebecormedia.com</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Salle de nouvelles</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>tvanouvelles.ca/nous-joindre</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 sept!</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
+Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
+Chaleureusement,
+__
+Gabriel Gouveia
+Co-fondateur
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L275" s="5" t="n"/>
+      <c r="M275" s="5" t="n"/>
+      <c r="N275" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N251"/>
+  <autoFilter ref="A1:N275"/>
   <dataValidations count="2">
-    <dataValidation sqref="N2:N251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N275" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"à réécrire au complet,à corriger,bon,ne pas envoyer"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I275" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"tu,vous,—"</formula1>
     </dataValidation>
   </dataValidations>

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Brouillons à éditer" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$275</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$290</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N275"/>
+  <dimension ref="A1:N290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17935,50 +17935,1145 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
+          <t>Global Toronto</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Global Toronto</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>viewercontacttoronto@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Pupitre de Toronto</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L254" s="5" t="n"/>
+      <c r="M254" s="5" t="n"/>
+      <c r="N254" s="6" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Global Calgary</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Global Calgary</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>calgary@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Pupitre de Calgary</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L255" s="5" t="n"/>
+      <c r="M255" s="5" t="n"/>
+      <c r="N255" s="6" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Global Edmonton</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Global Edmonton</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>edmonton@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Pupitre d'Edmonton</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L256" s="5" t="n"/>
+      <c r="M256" s="5" t="n"/>
+      <c r="N256" s="6" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Global Winnipeg</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Global Winnipeg</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>winnipeg@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Pupitre de Winnipeg</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L257" s="5" t="n"/>
+      <c r="M257" s="5" t="n"/>
+      <c r="N257" s="6" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Global Halifax</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Global Halifax</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>halifax@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Pupitre d'Halifax</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L258" s="5" t="n"/>
+      <c r="M258" s="5" t="n"/>
+      <c r="N258" s="6" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Global Regina</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Global Regina</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>regina@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Pupitre de Regina</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L259" s="5" t="n"/>
+      <c r="M259" s="5" t="n"/>
+      <c r="N259" s="6" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Global Saskatoon</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Global Saskatoon</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>saskatoon@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Pupitre de Saskatoon</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L260" s="5" t="n"/>
+      <c r="M260" s="5" t="n"/>
+      <c r="N260" s="6" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Global Okanagan</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Global Okanagan</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>okanagan@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Pupitre de l'Okanagan</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L261" s="5" t="n"/>
+      <c r="M261" s="5" t="n"/>
+      <c r="N261" s="6" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Global — Consumer Matters</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Global — Consumer Matters</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>consumermatters@globalnews.ca</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Chronique consommation</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>A $300 winter coat insulated with a farm weed instead of down or polyester — the consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+A $300 winter coat insulated with a farm weed instead of down or polyester — the consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L262" s="5" t="n"/>
+      <c r="M262" s="5" t="n"/>
+      <c r="N262" s="6" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Daily Hive Vancouver</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Daily Hive Vancouver</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>vancouver@dailyhive.com</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Pupitre de Vancouver</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L263" s="5" t="n"/>
+      <c r="M263" s="5" t="n"/>
+      <c r="N263" s="6" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Daily Hive Toronto</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Daily Hive Toronto</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>toronto@dailyhive.com</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Pupitre de Toronto</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L264" s="5" t="n"/>
+      <c r="M264" s="5" t="n"/>
+      <c r="N264" s="6" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Daily Hive Calgary</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Daily Hive Calgary</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>calgary@dailyhive.com</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Pupitre de Calgary</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L265" s="5" t="n"/>
+      <c r="M265" s="5" t="n"/>
+      <c r="N265" s="6" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Daily Hive Edmonton</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Daily Hive Edmonton</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>edmonton@dailyhive.com</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Pupitre d'Edmonton</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L266" s="5" t="n"/>
+      <c r="M266" s="5" t="n"/>
+      <c r="N266" s="6" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Taproot Edmonton</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Taproot Edmonton</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>info@taproot.ca</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L267" s="5" t="n"/>
+      <c r="M267" s="5" t="n"/>
+      <c r="N267" s="6" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Textile World</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Textile World</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>jdavis@textileworld.com</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments, which is the part nobody had managed to hold.</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments, which is the part nobody had managed to hold.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="n"/>
+      <c r="M268" s="5" t="n"/>
+      <c r="N268" s="6" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
           <t>Better Farming</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C269" t="inlineStr">
         <is>
           <t>Better Farming</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>editor@betterfarming.com</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F269" t="inlineStr">
         <is>
           <t>Rédaction</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest — that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H269" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J254" s="2" t="inlineStr">
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
         <is>
           <t>Quebec milkweed on Dragons' Den — this Thursday</t>
         </is>
       </c>
-      <c r="K254" s="2" t="inlineStr">
+      <c r="K269" s="2" t="inlineStr">
         <is>
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
@@ -17996,57 +19091,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L254" s="5" t="n"/>
-      <c r="M254" s="5" t="n"/>
-      <c r="N254" s="6" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="L269" s="5" t="n"/>
+      <c r="M269" s="5" t="n"/>
+      <c r="N269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>Johanne Lapierre</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C270" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>johanne.j.lapierre@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F270" t="inlineStr">
         <is>
           <t>Rédactrice en chef</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
+      <c r="H270" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J255" s="2" t="inlineStr">
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K255" s="2" t="inlineStr">
+      <c r="K270" s="2" t="inlineStr">
         <is>
           <t>Bonjour Johanne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18065,57 +19160,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L255" s="5" t="n"/>
-      <c r="M255" s="5" t="n"/>
-      <c r="N255" s="6" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="L270" s="5" t="n"/>
+      <c r="M270" s="5" t="n"/>
+      <c r="N270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>Catherine Mercier</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C271" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D271" t="inlineStr">
         <is>
           <t>catherine.mercier@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F271" t="inlineStr">
         <is>
           <t>Animatrice</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
+      <c r="H271" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J256" s="2" t="inlineStr">
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K256" s="2" t="inlineStr">
+      <c r="K271" s="2" t="inlineStr">
         <is>
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18134,57 +19229,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L256" s="5" t="n"/>
-      <c r="M256" s="5" t="n"/>
-      <c r="N256" s="6" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="L271" s="5" t="n"/>
+      <c r="M271" s="5" t="n"/>
+      <c r="N271" s="6" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>France Beaudoin</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C272" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D272" t="inlineStr">
         <is>
           <t>france.beaudoin@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
+      <c r="F272" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
+      <c r="H272" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J257" s="2" t="inlineStr">
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K257" s="2" t="inlineStr">
+      <c r="K272" s="2" t="inlineStr">
         <is>
           <t>Bonjour France,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18203,57 +19298,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L257" s="5" t="n"/>
-      <c r="M257" s="5" t="n"/>
-      <c r="N257" s="6" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="L272" s="5" t="n"/>
+      <c r="M272" s="5" t="n"/>
+      <c r="N272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>Gilbert Bégin</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D273" t="inlineStr">
         <is>
           <t>gilbert.begin@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
+      <c r="H273" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J258" s="2" t="inlineStr">
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K258" s="2" t="inlineStr">
+      <c r="K273" s="2" t="inlineStr">
         <is>
           <t>Bonjour Gilbert,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18272,57 +19367,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L258" s="5" t="n"/>
-      <c r="M258" s="5" t="n"/>
-      <c r="N258" s="6" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="L273" s="5" t="n"/>
+      <c r="M273" s="5" t="n"/>
+      <c r="N273" s="6" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>Carine Monat</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D274" t="inlineStr">
         <is>
           <t>carine.monat@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
+      <c r="F274" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H274" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J259" s="2" t="inlineStr">
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K259" s="2" t="inlineStr">
+      <c r="K274" s="2" t="inlineStr">
         <is>
           <t>Bonjour Carine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18341,57 +19436,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L259" s="5" t="n"/>
-      <c r="M259" s="5" t="n"/>
-      <c r="N259" s="6" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="L274" s="5" t="n"/>
+      <c r="M274" s="5" t="n"/>
+      <c r="N274" s="6" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>Maxime Poiré</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C275" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D275" t="inlineStr">
         <is>
           <t>maxime.poire@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H275" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J260" s="2" t="inlineStr">
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K260" s="2" t="inlineStr">
+      <c r="K275" s="2" t="inlineStr">
         <is>
           <t>Bonjour Maxime,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18410,57 +19505,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L260" s="5" t="n"/>
-      <c r="M260" s="5" t="n"/>
-      <c r="N260" s="6" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="L275" s="5" t="n"/>
+      <c r="M275" s="5" t="n"/>
+      <c r="N275" s="6" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>Marie Maude Pontbriand</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D276" t="inlineStr">
         <is>
           <t>marie-maude.pontbriand@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H276" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J261" s="2" t="inlineStr">
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K261" s="2" t="inlineStr">
+      <c r="K276" s="2" t="inlineStr">
         <is>
           <t>Bonjour Marie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18479,57 +19574,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L261" s="5" t="n"/>
-      <c r="M261" s="5" t="n"/>
-      <c r="N261" s="6" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="L276" s="5" t="n"/>
+      <c r="M276" s="5" t="n"/>
+      <c r="N276" s="6" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>Julie Vaillancourt</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D277" t="inlineStr">
         <is>
           <t>julie.vaillancourt@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
+      <c r="G277" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H277" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J262" s="2" t="inlineStr">
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K262" s="2" t="inlineStr">
+      <c r="K277" s="2" t="inlineStr">
         <is>
           <t>Bonjour Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18548,57 +19643,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L262" s="5" t="n"/>
-      <c r="M262" s="5" t="n"/>
-      <c r="N262" s="6" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="L277" s="5" t="n"/>
+      <c r="M277" s="5" t="n"/>
+      <c r="N277" s="6" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>Marc-Yvan Hébert</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>marc-yvan.hebert@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>Journaliste-réalisateur</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="G278" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H278" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J263" s="2" t="inlineStr">
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K263" s="2" t="inlineStr">
+      <c r="K278" s="2" t="inlineStr">
         <is>
           <t>Bonjour Marc-Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18617,57 +19712,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L263" s="5" t="n"/>
-      <c r="M263" s="5" t="n"/>
-      <c r="N263" s="6" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="L278" s="5" t="n"/>
+      <c r="M278" s="5" t="n"/>
+      <c r="N278" s="6" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Benoit Livernoche</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>benoit.livernoche@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F279" t="inlineStr">
         <is>
           <t>Journaliste-réalisateur</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="G279" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H279" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J264" s="2" t="inlineStr">
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K264" s="2" t="inlineStr">
+      <c r="K279" s="2" t="inlineStr">
         <is>
           <t>Bonjour Benoit,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18686,57 +19781,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L264" s="5" t="n"/>
-      <c r="M264" s="5" t="n"/>
-      <c r="N264" s="6" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+      <c r="L279" s="5" t="n"/>
+      <c r="M279" s="5" t="n"/>
+      <c r="N279" s="6" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>TVA Nouvelles</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>TVA Nouvelles</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>nouvelles@tva.ca</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>Pupitre national</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="G280" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
+      <c r="H280" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J265" s="2" t="inlineStr">
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K265" s="2" t="inlineStr">
+      <c r="K280" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18755,57 +19850,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L265" s="5" t="n"/>
-      <c r="M265" s="5" t="n"/>
-      <c r="N265" s="6" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+      <c r="L280" s="5" t="n"/>
+      <c r="M280" s="5" t="n"/>
+      <c r="N280" s="6" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>TVA Québec</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>TVA Québec</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>nouvelles.quebec@tva.ca</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F281" t="inlineStr">
         <is>
           <t>Pupitre de Québec</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr">
+      <c r="G281" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H281" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J266" s="2" t="inlineStr">
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K266" s="2" t="inlineStr">
+      <c r="K281" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18824,57 +19919,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L266" s="5" t="n"/>
-      <c r="M266" s="5" t="n"/>
-      <c r="N266" s="6" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+      <c r="L281" s="5" t="n"/>
+      <c r="M281" s="5" t="n"/>
+      <c r="N281" s="6" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>TVA Saguenay</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>TVA Saguenay</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D282" t="inlineStr">
         <is>
           <t>nouvelles.cjpm@tva.ca</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>Pupitre du Saguenay</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr">
+      <c r="G282" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
+      <c r="H282" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J267" s="2" t="inlineStr">
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K267" s="2" t="inlineStr">
+      <c r="K282" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18893,57 +19988,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L267" s="5" t="n"/>
-      <c r="M267" s="5" t="n"/>
-      <c r="N267" s="6" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+      <c r="L282" s="5" t="n"/>
+      <c r="M282" s="5" t="n"/>
+      <c r="N282" s="6" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>TVA Trois-Rivières</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>TVA Trois-Rivières</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>nouvelles.chem@tva.ca</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>Pupitre de la Mauricie</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr">
+      <c r="G283" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
+      <c r="H283" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J268" s="2" t="inlineStr">
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K268" s="2" t="inlineStr">
+      <c r="K283" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -18962,57 +20057,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L268" s="5" t="n"/>
-      <c r="M268" s="5" t="n"/>
-      <c r="N268" s="6" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="L283" s="5" t="n"/>
+      <c r="M283" s="5" t="n"/>
+      <c r="N283" s="6" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>TVA Sherbrooke</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>TVA Sherbrooke</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>nouvelles.sherbrooke@tva.ca</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>Pupitre de l'Estrie</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr">
+      <c r="G284" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
+      <c r="H284" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J269" s="2" t="inlineStr">
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K269" s="2" t="inlineStr">
+      <c r="K284" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19031,57 +20126,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L269" s="5" t="n"/>
-      <c r="M269" s="5" t="n"/>
-      <c r="N269" s="6" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="L284" s="5" t="n"/>
+      <c r="M284" s="5" t="n"/>
+      <c r="N284" s="6" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>TVA Est-du-Québec</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C285" t="inlineStr">
         <is>
           <t>TVA Est-du-Québec</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D285" t="inlineStr">
         <is>
           <t>nouvelles.cfer@tva.ca</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
+      <c r="F285" t="inlineStr">
         <is>
           <t>Pupitre de l'Est-du-Québec</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr">
+      <c r="G285" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
+      <c r="H285" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J270" s="2" t="inlineStr">
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K270" s="2" t="inlineStr">
+      <c r="K285" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19100,57 +20195,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L270" s="5" t="n"/>
-      <c r="M270" s="5" t="n"/>
-      <c r="N270" s="6" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+      <c r="L285" s="5" t="n"/>
+      <c r="M285" s="5" t="n"/>
+      <c r="N285" s="6" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>Québecor Québec</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t>Québecor Québec</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D286" t="inlineStr">
         <is>
           <t>quebec@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F286" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="G286" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="H286" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J271" s="2" t="inlineStr">
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K271" s="2" t="inlineStr">
+      <c r="K286" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19169,57 +20264,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L271" s="5" t="n"/>
-      <c r="M271" s="5" t="n"/>
-      <c r="N271" s="6" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="L286" s="5" t="n"/>
+      <c r="M286" s="5" t="n"/>
+      <c r="N286" s="6" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>Québecor Montréal</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>Québecor Montréal</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D287" t="inlineStr">
         <is>
           <t>montreal@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr">
+      <c r="G287" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
+      <c r="H287" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J272" s="2" t="inlineStr">
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K272" s="2" t="inlineStr">
+      <c r="K287" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19238,57 +20333,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L272" s="5" t="n"/>
-      <c r="M272" s="5" t="n"/>
-      <c r="N272" s="6" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="L287" s="5" t="n"/>
+      <c r="M287" s="5" t="n"/>
+      <c r="N287" s="6" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>Québecor Sherbrooke</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>Québecor Sherbrooke</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D288" t="inlineStr">
         <is>
           <t>sherbrooke@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr">
+      <c r="G288" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
+      <c r="H288" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J273" s="2" t="inlineStr">
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K273" s="2" t="inlineStr">
+      <c r="K288" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19307,57 +20402,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L273" s="5" t="n"/>
-      <c r="M273" s="5" t="n"/>
-      <c r="N273" s="6" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="L288" s="5" t="n"/>
+      <c r="M288" s="5" t="n"/>
+      <c r="N288" s="6" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>Québecor Trois-Rivières</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C289" t="inlineStr">
         <is>
           <t>Québecor Trois-Rivières</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D289" t="inlineStr">
         <is>
           <t>trois-rivieres@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
+      <c r="G289" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
+      <c r="H289" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J274" s="2" t="inlineStr">
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K274" s="2" t="inlineStr">
+      <c r="K289" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19376,57 +20471,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L274" s="5" t="n"/>
-      <c r="M274" s="5" t="n"/>
-      <c r="N274" s="6" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="L289" s="5" t="n"/>
+      <c r="M289" s="5" t="n"/>
+      <c r="N289" s="6" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>Québecor Est-du-Québec</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>Québecor Est-du-Québec</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D290" t="inlineStr">
         <is>
           <t>estquebec@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr">
+      <c r="G290" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
+      <c r="H290" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J275" s="2" t="inlineStr">
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K275" s="2" t="inlineStr">
+      <c r="K290" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19445,17 +20540,17 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L275" s="5" t="n"/>
-      <c r="M275" s="5" t="n"/>
-      <c r="N275" s="6" t="n"/>
+      <c r="L290" s="5" t="n"/>
+      <c r="M290" s="5" t="n"/>
+      <c r="N290" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N275"/>
+  <autoFilter ref="A1:N290"/>
   <dataValidations count="2">
-    <dataValidation sqref="N2:N275" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"à réécrire au complet,à corriger,bon,ne pas envoyer"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I275" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"tu,vous,—"</formula1>
     </dataValidation>
   </dataValidations>

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -17172,18 +17172,18 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 I'm writing to the wire first because if this is worth two paragraphs, it's worth them in every paper in the country: a Quebec company insulating winter coats with the only plant monarch caterpillars can eat is going on national television Thursday.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17245,18 +17245,18 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 The business story: we built our own processing because no subcontractor would touch the fibre, changed our manufacturing model last year to survive, and are now pitching on national television.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17318,18 +17318,18 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17376,7 +17376,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -17391,18 +17391,18 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17449,7 +17449,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -17464,18 +17464,18 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars eat.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17522,7 +17522,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — Thursday's national broadcast is a local story first.</t>
+          <t>We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here, Thursday's national broadcast is a local story first.</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -17537,18 +17537,18 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here — Thursday's national broadcast is a local story first.
+We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here, Thursday's national broadcast is a local story first.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17595,7 +17595,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.</t>
+          <t>We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields. The coat on the shelf begins as a pod in a row of weeds somebody decided not to spray.</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -17610,18 +17610,18 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields — a retail story as much as an environmental one.
+We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields. The coat on the shelf begins as a pod in a row of weeds somebody decided not to spray.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17668,7 +17668,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments — which makes us, as far as we know, the only ones doing the whole chain.</t>
+          <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -17683,18 +17683,18 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments — which makes us, as far as we know, the only ones doing the whole chain.
+You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17756,18 +17756,18 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17814,7 +17814,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments, which is the part nobody had managed to hold.</t>
+          <t>Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments. That last step is where the earlier attempts stopped.</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -17829,18 +17829,18 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments, which is the part nobody had managed to hold.
+Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments. That last step is where the earlier attempts stopped.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17902,18 +17902,18 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Plant-based insulation is one of the few places where outerwear can actually leave animal and petroleum fibres behind, and milkweed is the rare one that also feeds a threatened pollinator.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -17960,7 +17960,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -17975,18 +17975,18 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18033,7 +18033,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -18048,18 +18048,18 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18106,7 +18106,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -18121,18 +18121,18 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18179,7 +18179,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -18194,18 +18194,18 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18252,7 +18252,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -18267,18 +18267,18 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18325,7 +18325,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -18340,18 +18340,18 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18398,7 +18398,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -18413,18 +18413,18 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18471,7 +18471,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
+          <t>A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -18486,18 +18486,18 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray — and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
+A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18519,12 +18519,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Global — Consumer Matters</t>
+          <t>Global, Consumer Matters</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Global — Consumer Matters</t>
+          <t>Global, Consumer Matters</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>A $300 winter coat insulated with a farm weed instead of down or polyester — the consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.</t>
+          <t>A $300 winter coat insulated with a farm weed instead of down or polyester. The consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -18559,18 +18559,18 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-A $300 winter coat insulated with a farm weed instead of down or polyester — the consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.
+A $300 winter coat insulated with a farm weed instead of down or polyester. The consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18617,7 +18617,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+          <t>Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -18632,18 +18632,18 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18690,7 +18690,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+          <t>Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -18705,18 +18705,18 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+          <t>Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -18778,18 +18778,18 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18836,7 +18836,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+          <t>Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -18851,18 +18851,18 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.</t>
+          <t>Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -18924,18 +18924,18 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-Your readers can watch it Thursday night, and the coat itself is Canadian all the way down: milkweed grown by Quebec farmers, floss processed into insulation in Quebec City, sold from coast to coast.
+Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -18997,18 +18997,18 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments, which is the part nobody had managed to hold.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -19055,7 +19055,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest — that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.</t>
+          <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest, that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -19070,18 +19070,18 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>Quebec milkweed on Dragons' Den — this Thursday</t>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
           <t>Hello,
-My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed — milkweed — that we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest — that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.
+The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest, that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it — or a colleague might — our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
-I'm genuinely hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
 __
@@ -19146,7 +19146,7 @@
           <t>Bonjour Johanne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19215,7 +19215,7 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19284,7 +19284,7 @@
           <t>Bonjour France,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19353,7 +19353,7 @@
           <t>Bonjour Gilbert,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19422,7 +19422,7 @@
           <t>Bonjour Carine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19491,7 +19491,7 @@
           <t>Bonjour Maxime,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19560,7 +19560,7 @@
           <t>Bonjour Marie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19629,7 +19629,7 @@
           <t>Bonjour Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19698,7 +19698,7 @@
           <t>Bonjour Marc-Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19767,7 +19767,7 @@
           <t>Bonjour Benoit,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre — s'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Brouillons à éditer" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$296</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N290"/>
+  <dimension ref="A1:N296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2303,7 +2303,7 @@
           <t>Bonjour Zoé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -2510,7 +2510,7 @@
           <t>Bonjour Normand,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -3062,7 +3062,7 @@
           <t>Bonjour Tristan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3131,7 +3131,7 @@
           <t>Bonjour Jean-Marc,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -3200,7 +3200,7 @@
           <t>Bonjour Simon,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -3269,7 +3269,7 @@
           <t>Bonjour Maxime,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3407,7 +3407,7 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -3613,7 +3613,7 @@
           <t>Bonjour Simon,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -3820,7 +3820,7 @@
           <t>Bonjour Myriam,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -4303,7 +4303,7 @@
           <t>Bonjour Pauline,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -4441,7 +4441,7 @@
           <t>Bonjour Leïla,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -4579,7 +4579,7 @@
           <t>Bonjour Annie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -4648,7 +4648,7 @@
           <t>Bonjour Marianne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -4717,7 +4717,7 @@
           <t>Bonjour Sophie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -5131,7 +5131,7 @@
           <t>Bonjour Annie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -5199,7 +5199,7 @@
         <is>
           <t>Bonjour Réjean,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment industriel au Québec. L'usine achetait 90 % des récoltes de la province avant que la filière se casse en 2018.
+Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment industriel au Québec. L'usine achetait 90 % des récoltes de la province avant que la filière se casse le 11 octobre 2017.
 On a démarré après. Six ans plus tard, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5338,7 +5338,7 @@
           <t>Bonjour Clara,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -5407,7 +5407,7 @@
           <t>Bonjour Valérian,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -5545,7 +5545,7 @@
           <t>Bonjour Nicolas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -5614,7 +5614,7 @@
           <t>Bonjour Nicolas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -5683,7 +5683,7 @@
           <t>Bonjour Véronique,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -6097,7 +6097,7 @@
           <t>Bonjour Josée,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -6166,7 +6166,7 @@
           <t>Bonjour Yannick,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -6373,7 +6373,7 @@
           <t>Bonjour Marie-Hélène,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -6718,7 +6718,7 @@
           <t>Bonjour Scott,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -6787,7 +6787,7 @@
           <t>Bonjour Michèle,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -6925,7 +6925,7 @@
           <t>Bonjour Karine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -7270,7 +7270,7 @@
           <t>Bonjour MARC-OLIVIER,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -7615,7 +7615,7 @@
           <t>Bonjour Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -7684,7 +7684,7 @@
           <t>Bonjour Gilles,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -7753,7 +7753,7 @@
           <t>Bonjour Daphné,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -7960,7 +7960,7 @@
           <t>Bonjour Sarah,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -8305,7 +8305,7 @@
           <t>Bonjour Amélie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
@@ -8374,7 +8374,7 @@
           <t>Bonjour Dominique,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -8512,7 +8512,7 @@
           <t>Bonjour Ève,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -8719,7 +8719,7 @@
           <t>Bonjour Raymond,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -8857,7 +8857,7 @@
           <t>Bonjour Marie-Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -8926,7 +8926,8 @@
           <t>Bonjour Chloé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -9271,7 +9272,8 @@
           <t>Bonjour Jacinthe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -9340,7 +9342,7 @@
           <t>Bonjour Bruno,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
@@ -9409,7 +9411,7 @@
           <t>Bonjour Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
@@ -9478,7 +9480,7 @@
           <t>Bonjour Yves,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
@@ -9616,7 +9618,7 @@
           <t>Bonjour Stéphanie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -9685,7 +9687,7 @@
           <t>Bonjour Philippe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -9754,7 +9756,7 @@
           <t>Bonjour Gildas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -10030,7 +10032,7 @@
           <t>Bonjour Geneviève,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -10099,7 +10101,7 @@
           <t>Bonjour Carole,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -10444,7 +10446,7 @@
           <t>Bonjour Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
@@ -10513,7 +10515,7 @@
           <t>Bonjour Katherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
@@ -10582,7 +10584,7 @@
           <t>Bonjour Michel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
@@ -10858,7 +10860,8 @@
           <t>Bonjour Anick,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
@@ -10927,7 +10930,7 @@
           <t>Bonjour Félix-Antoine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
@@ -11065,7 +11068,7 @@
           <t>Bonjour Julia,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
@@ -11134,7 +11137,7 @@
           <t>Bonjour Karine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
@@ -11410,7 +11413,7 @@
           <t>Bonjour Bernard,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
@@ -12169,7 +12172,7 @@
           <t>Bonjour Kathleen,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -12652,7 +12655,7 @@
           <t>Bonjour Thomas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -13135,7 +13138,7 @@
           <t>Bonjour Maxim,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
@@ -13608,10 +13611,23 @@
           <t>vous</t>
         </is>
       </c>
-      <c r="J191" s="2" t="n"/>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>NE PAS ENVOYER — doublon de la liste chaude. Le message écrit à la main a préséance.</t>
+          <t>Bonjour Francis,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
       <c r="L191" s="5" t="n"/>
@@ -14009,10 +14025,23 @@
           <t>vous</t>
         </is>
       </c>
-      <c r="J197" s="2" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>NE PAS ENVOYER — doublon de la liste chaude. Le message écrit à la main a préséance.</t>
+          <t>Bonjour Annie,
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
+Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
+Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
       <c r="L197" s="5" t="n"/>
@@ -14903,7 +14932,7 @@
           <t>Bonjour Timothy,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
@@ -15110,7 +15139,7 @@
           <t>Bonjour MELISSA,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -15179,7 +15208,7 @@
           <t>Bonjour Isaac,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -15869,7 +15898,7 @@
           <t>Bonjour Louis-Philippe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -16283,7 +16312,7 @@
           <t>Bonjour Kimberley,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -16352,7 +16381,7 @@
           <t>Bonjour William,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
@@ -16766,7 +16795,8 @@
           <t>Bonjour Paule,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -17668,7 +17698,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain.</t>
+          <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain. The Quebec filière collapsed on October 11, 2017 when the group that had reserved 90 per cent of the crop went bankrupt (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), which is the context for anything written about milkweed insulation today.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -17691,7 +17721,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain.
+You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain. The Quebec filière collapsed on October 11, 2017 when the group that had reserved 90 per cent of the crop went bankrupt (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), which is the context for anything written about milkweed insulation today.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
@@ -19030,17 +19060,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Better Farming</t>
+          <t>Huddle</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Better Farming</t>
+          <t>Huddle</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>editor@betterfarming.com</t>
+          <t>news@huddle.today</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -19050,12 +19080,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Rédaction</t>
+          <t>Nouvelles d'affaires du Nouveau-Brunswick</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest, that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.</t>
+          <t>The business angle from the Atlantic side: we built our own processing because no subcontractor would touch the fibre, and we are about to pitch it on national television. Atlantic Canada has the same problem we had, a raw material with no processing chain.</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -19078,7 +19108,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. We still buy the harvest, that's the part that collapsed in 2018 and the part that decides whether anyone plants it again.
+The business angle from the Atlantic side: we built our own processing because no subcontractor would touch the fibre, and we are about to pitch it on national television. Atlantic Canada has the same problem we had, a raw material with no processing chain.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
@@ -19098,55 +19128,494 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Nunatsiaq News</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Nunatsiaq News</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>editors@nunatsiaq.com</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="n"/>
+      <c r="M270" s="5" t="n"/>
+      <c r="N270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Cabin Radio</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Cabin Radio</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>sarah@cabinradio.ca</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Rédaction, T.N.-O.</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L271" s="5" t="n"/>
+      <c r="M271" s="5" t="n"/>
+      <c r="N271" s="6" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>NNSL Media</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>NNSL Media</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>newsroom@nnsl.com</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Salle de nouvelles, T.N.-O. et Nunavut</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L272" s="5" t="n"/>
+      <c r="M272" s="5" t="n"/>
+      <c r="N272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Yukon News</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Yukon News</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>newstips@yukon-news.com</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Ligne de nouvelles</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L273" s="5" t="n"/>
+      <c r="M273" s="5" t="n"/>
+      <c r="N273" s="6" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>NB Media Co-op</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>NB Media Co-op</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>info@nbmediacoop.org</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>The farm side of it: milkweed is a weed most growers spray, and a Quebec cooperative of 125 producers lost its only buyer overnight in 2017. We still buy the harvest. That question, whether anyone is waiting at the end of the field, is not specific to Quebec.</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+The farm side of it: milkweed is a weed most growers spray, and a Quebec cooperative of 125 producers lost its only buyer overnight in 2017. We still buy the harvest. That question, whether anyone is waiting at the end of the field, is not specific to Quebec.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L274" s="5" t="n"/>
+      <c r="M274" s="5" t="n"/>
+      <c r="N274" s="6" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>anglo</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Better Farming</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Better Farming</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>editor@betterfarming.com</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Rédaction</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. It stopped on October 11, 2017, when the group that had reserved 90 per cent of the Quebec crop went bankrupt and 125 growers lost their buyer overnight (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). We still buy the harvest, and that is the part that decides whether anyone plants it again.</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>Quebec milkweed on Dragons' Den, this Thursday</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
+Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. It stopped on October 11, 2017, when the group that had reserved 90 per cent of the Quebec crop went bankrupt and 125 growers lost their buyer overnight (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). We still buy the harvest, and that is the part that decides whether anyone plants it again.
+This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
+If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
+Happy to answer any questions, and available for an interview this week.
+Warmly,
+__
+Gabriel Gouveia
+Co-founder
++1 (581) 982-5857
+Lasclay.com</t>
+        </is>
+      </c>
+      <c r="L275" s="5" t="n"/>
+      <c r="M275" s="5" t="n"/>
+      <c r="N275" s="6" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>Johanne Lapierre</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D276" t="inlineStr">
         <is>
           <t>johanne.j.lapierre@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>Rédactrice en chef</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
+      <c r="H276" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J270" s="2" t="inlineStr">
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K270" s="2" t="inlineStr">
+      <c r="K276" s="2" t="inlineStr">
         <is>
           <t>Bonjour Johanne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19160,62 +19629,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L270" s="5" t="n"/>
-      <c r="M270" s="5" t="n"/>
-      <c r="N270" s="6" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+      <c r="L276" s="5" t="n"/>
+      <c r="M276" s="5" t="n"/>
+      <c r="N276" s="6" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>Catherine Mercier</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D277" t="inlineStr">
         <is>
           <t>catherine.mercier@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>Animatrice</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="G277" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="H277" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J271" s="2" t="inlineStr">
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K271" s="2" t="inlineStr">
+      <c r="K277" s="2" t="inlineStr">
         <is>
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19229,62 +19699,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L271" s="5" t="n"/>
-      <c r="M271" s="5" t="n"/>
-      <c r="N271" s="6" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="L277" s="5" t="n"/>
+      <c r="M277" s="5" t="n"/>
+      <c r="N277" s="6" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>France Beaudoin</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>france.beaudoin@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr">
+      <c r="G278" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
+      <c r="H278" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J272" s="2" t="inlineStr">
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K272" s="2" t="inlineStr">
+      <c r="K278" s="2" t="inlineStr">
         <is>
           <t>Bonjour France,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19298,62 +19769,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L272" s="5" t="n"/>
-      <c r="M272" s="5" t="n"/>
-      <c r="N272" s="6" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="L278" s="5" t="n"/>
+      <c r="M278" s="5" t="n"/>
+      <c r="N278" s="6" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Gilbert Bégin</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>gilbert.begin@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F279" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr">
+      <c r="G279" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
+      <c r="H279" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J273" s="2" t="inlineStr">
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K273" s="2" t="inlineStr">
+      <c r="K279" s="2" t="inlineStr">
         <is>
           <t>Bonjour Gilbert,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19367,62 +19839,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L273" s="5" t="n"/>
-      <c r="M273" s="5" t="n"/>
-      <c r="N273" s="6" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="L279" s="5" t="n"/>
+      <c r="M279" s="5" t="n"/>
+      <c r="N279" s="6" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>Carine Monat</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>carine.monat@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
+      <c r="G280" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
+      <c r="H280" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J274" s="2" t="inlineStr">
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K274" s="2" t="inlineStr">
+      <c r="K280" s="2" t="inlineStr">
         <is>
           <t>Bonjour Carine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19436,62 +19909,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L274" s="5" t="n"/>
-      <c r="M274" s="5" t="n"/>
-      <c r="N274" s="6" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="L280" s="5" t="n"/>
+      <c r="M280" s="5" t="n"/>
+      <c r="N280" s="6" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>Maxime Poiré</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>maxime.poire@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
+      <c r="F281" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr">
+      <c r="G281" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
+      <c r="H281" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J275" s="2" t="inlineStr">
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K275" s="2" t="inlineStr">
+      <c r="K281" s="2" t="inlineStr">
         <is>
           <t>Bonjour Maxime,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19505,62 +19979,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L275" s="5" t="n"/>
-      <c r="M275" s="5" t="n"/>
-      <c r="N275" s="6" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="L281" s="5" t="n"/>
+      <c r="M281" s="5" t="n"/>
+      <c r="N281" s="6" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>Marie Maude Pontbriand</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D282" t="inlineStr">
         <is>
           <t>marie-maude.pontbriand@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr">
+      <c r="G282" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
+      <c r="H282" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J276" s="2" t="inlineStr">
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K276" s="2" t="inlineStr">
+      <c r="K282" s="2" t="inlineStr">
         <is>
           <t>Bonjour Marie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19574,62 +20049,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L276" s="5" t="n"/>
-      <c r="M276" s="5" t="n"/>
-      <c r="N276" s="6" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+      <c r="L282" s="5" t="n"/>
+      <c r="M282" s="5" t="n"/>
+      <c r="N282" s="6" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>Julie Vaillancourt</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>julie.vaillancourt@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>Journaliste</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr">
+      <c r="G283" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
+      <c r="H283" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J277" s="2" t="inlineStr">
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K277" s="2" t="inlineStr">
+      <c r="K283" s="2" t="inlineStr">
         <is>
           <t>Bonjour Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19643,62 +20119,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L277" s="5" t="n"/>
-      <c r="M277" s="5" t="n"/>
-      <c r="N277" s="6" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="L283" s="5" t="n"/>
+      <c r="M283" s="5" t="n"/>
+      <c r="N283" s="6" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>Marc-Yvan Hébert</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>marc-yvan.hebert@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>Journaliste-réalisateur</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr">
+      <c r="G284" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
+      <c r="H284" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J278" s="2" t="inlineStr">
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K278" s="2" t="inlineStr">
+      <c r="K284" s="2" t="inlineStr">
         <is>
           <t>Bonjour Marc-Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19712,62 +20189,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L278" s="5" t="n"/>
-      <c r="M278" s="5" t="n"/>
-      <c r="N278" s="6" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
+      <c r="L284" s="5" t="n"/>
+      <c r="M284" s="5" t="n"/>
+      <c r="N284" s="6" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>Benoit Livernoche</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C285" t="inlineStr">
         <is>
           <t>La Semaine verte (Radio-Canada)</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D285" t="inlineStr">
         <is>
           <t>benoit.livernoche@radio-canada.ca</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
+      <c r="F285" t="inlineStr">
         <is>
           <t>Journaliste-réalisateur</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr">
+      <c r="G285" s="2" t="inlineStr">
         <is>
           <t>ici.radio-canada.ca/tele/la-semaine-verte</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
+      <c r="H285" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J279" s="2" t="inlineStr">
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K279" s="2" t="inlineStr">
+      <c r="K285" s="2" t="inlineStr">
         <is>
           <t>Bonjour Benoit,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est d'abord une histoire agricole. La filière s'est cassée en 2018 quand l'usine de Saint-Tite a fermé, et la question n'a pas changé depuis : y a-t-il un acheteur stable au bout du champ. Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur au Lac-Saint-Jean, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19781,57 +20259,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L279" s="5" t="n"/>
-      <c r="M279" s="5" t="n"/>
-      <c r="N279" s="6" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
+      <c r="L285" s="5" t="n"/>
+      <c r="M285" s="5" t="n"/>
+      <c r="N285" s="6" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>TVA Nouvelles</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t>TVA Nouvelles</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D286" t="inlineStr">
         <is>
           <t>nouvelles@tva.ca</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F286" t="inlineStr">
         <is>
           <t>Pupitre national</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr">
+      <c r="G286" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
+      <c r="H286" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J280" s="2" t="inlineStr">
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K280" s="2" t="inlineStr">
+      <c r="K286" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19850,57 +20328,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L280" s="5" t="n"/>
-      <c r="M280" s="5" t="n"/>
-      <c r="N280" s="6" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
+      <c r="L286" s="5" t="n"/>
+      <c r="M286" s="5" t="n"/>
+      <c r="N286" s="6" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>TVA Québec</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>TVA Québec</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D287" t="inlineStr">
         <is>
           <t>nouvelles.quebec@tva.ca</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>Pupitre de Québec</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr">
+      <c r="G287" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
+      <c r="H287" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J281" s="2" t="inlineStr">
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K281" s="2" t="inlineStr">
+      <c r="K287" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -19919,62 +20397,62 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L281" s="5" t="n"/>
-      <c r="M281" s="5" t="n"/>
-      <c r="N281" s="6" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
+      <c r="L287" s="5" t="n"/>
+      <c r="M287" s="5" t="n"/>
+      <c r="N287" s="6" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>TVA Saguenay</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>TVA Saguenay</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D288" t="inlineStr">
         <is>
           <t>nouvelles.cjpm@tva.ca</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>Pupitre du Saguenay</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr">
+      <c r="G288" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
+      <c r="H288" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J282" s="2" t="inlineStr">
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K282" s="2" t="inlineStr">
+      <c r="K288" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Notre fournisseur du Lac-Saint-Jean, Sabin Tremblay de L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts.
+Je vous écris parce que Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive de l'asclépiade pour nous depuis nos tout débuts, et qu'il en cultive encore. Je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -19988,62 +20466,63 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L282" s="5" t="n"/>
-      <c r="M282" s="5" t="n"/>
-      <c r="N282" s="6" t="n"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
+      <c r="L288" s="5" t="n"/>
+      <c r="M288" s="5" t="n"/>
+      <c r="N288" s="6" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>TVA Trois-Rivières</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C289" t="inlineStr">
         <is>
           <t>TVA Trois-Rivières</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D289" t="inlineStr">
         <is>
           <t>nouvelles.chem@tva.ca</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>Pupitre de la Mauricie</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr">
+      <c r="G289" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
+      <c r="H289" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J283" s="2" t="inlineStr">
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K283" s="2" t="inlineStr">
+      <c r="K289" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-L'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018.
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -20057,62 +20536,62 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L283" s="5" t="n"/>
-      <c r="M283" s="5" t="n"/>
-      <c r="N283" s="6" t="n"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
+      <c r="L289" s="5" t="n"/>
+      <c r="M289" s="5" t="n"/>
+      <c r="N289" s="6" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>TVA Sherbrooke</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>TVA Sherbrooke</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D290" t="inlineStr">
         <is>
           <t>nouvelles.sherbrooke@tva.ca</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>Pupitre de l'Estrie</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr">
+      <c r="G290" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
+      <c r="H290" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J284" s="2" t="inlineStr">
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K284" s="2" t="inlineStr">
+      <c r="K290" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Une des premières usines de transformation de la fibre était à Granby, et l'Estrie compte encore des producteurs d'asclépiade.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
 Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
@@ -20126,57 +20605,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L284" s="5" t="n"/>
-      <c r="M284" s="5" t="n"/>
-      <c r="N284" s="6" t="n"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
+      <c r="L290" s="5" t="n"/>
+      <c r="M290" s="5" t="n"/>
+      <c r="N290" s="6" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>TVA Est-du-Québec</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C291" t="inlineStr">
         <is>
           <t>TVA Est-du-Québec</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D291" t="inlineStr">
         <is>
           <t>nouvelles.cfer@tva.ca</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
+      <c r="F291" t="inlineStr">
         <is>
           <t>Pupitre de l'Est-du-Québec</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr">
+      <c r="G291" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
+      <c r="H291" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J285" s="2" t="inlineStr">
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K285" s="2" t="inlineStr">
+      <c r="K291" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -20195,57 +20674,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L285" s="5" t="n"/>
-      <c r="M285" s="5" t="n"/>
-      <c r="N285" s="6" t="n"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
+      <c r="L291" s="5" t="n"/>
+      <c r="M291" s="5" t="n"/>
+      <c r="N291" s="6" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>Québecor Québec</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C292" t="inlineStr">
         <is>
           <t>Québecor Québec</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D292" t="inlineStr">
         <is>
           <t>quebec@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
+      <c r="F292" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr">
+      <c r="G292" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
+      <c r="H292" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J286" s="2" t="inlineStr">
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K286" s="2" t="inlineStr">
+      <c r="K292" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -20264,57 +20743,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L286" s="5" t="n"/>
-      <c r="M286" s="5" t="n"/>
-      <c r="N286" s="6" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
+      <c r="L292" s="5" t="n"/>
+      <c r="M292" s="5" t="n"/>
+      <c r="N292" s="6" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>Québecor Montréal</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
+      <c r="C293" t="inlineStr">
         <is>
           <t>Québecor Montréal</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="D293" t="inlineStr">
         <is>
           <t>montreal@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
+      <c r="F293" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr">
+      <c r="G293" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
+      <c r="H293" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J287" s="2" t="inlineStr">
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K287" s="2" t="inlineStr">
+      <c r="K293" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -20333,57 +20812,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L287" s="5" t="n"/>
-      <c r="M287" s="5" t="n"/>
-      <c r="N287" s="6" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
+      <c r="L293" s="5" t="n"/>
+      <c r="M293" s="5" t="n"/>
+      <c r="N293" s="6" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>Québecor Sherbrooke</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C294" t="inlineStr">
         <is>
           <t>Québecor Sherbrooke</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D294" t="inlineStr">
         <is>
           <t>sherbrooke@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
+      <c r="F294" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr">
+      <c r="G294" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
+      <c r="H294" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J288" s="2" t="inlineStr">
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K288" s="2" t="inlineStr">
+      <c r="K294" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -20402,57 +20881,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L288" s="5" t="n"/>
-      <c r="M288" s="5" t="n"/>
-      <c r="N288" s="6" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
+      <c r="L294" s="5" t="n"/>
+      <c r="M294" s="5" t="n"/>
+      <c r="N294" s="6" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>Québecor Trois-Rivières</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
+      <c r="C295" t="inlineStr">
         <is>
           <t>Québecor Trois-Rivières</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D295" t="inlineStr">
         <is>
           <t>trois-rivieres@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
+      <c r="F295" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr">
+      <c r="G295" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
+      <c r="H295" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J289" s="2" t="inlineStr">
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K289" s="2" t="inlineStr">
+      <c r="K295" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -20471,57 +20950,57 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L289" s="5" t="n"/>
-      <c r="M289" s="5" t="n"/>
-      <c r="N289" s="6" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
+      <c r="L295" s="5" t="n"/>
+      <c r="M295" s="5" t="n"/>
+      <c r="N295" s="6" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
         <is>
           <t>ajout</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t>Québecor Est-du-Québec</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
+      <c r="C296" t="inlineStr">
         <is>
           <t>Québecor Est-du-Québec</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="D296" t="inlineStr">
         <is>
           <t>estquebec@quebecormedia.com</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
+      <c r="F296" t="inlineStr">
         <is>
           <t>Salle de nouvelles</t>
         </is>
       </c>
-      <c r="G290" s="2" t="inlineStr">
+      <c r="G296" s="2" t="inlineStr">
         <is>
           <t>tvanouvelles.ca/nous-joindre</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
+      <c r="H296" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>vous</t>
-        </is>
-      </c>
-      <c r="J290" s="2" t="inlineStr">
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>vous</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
         <is>
           <t>L'asclépiade à Dragons' Den le 17 sept!</t>
         </is>
       </c>
-      <c r="K290" s="2" t="inlineStr">
+      <c r="K296" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
@@ -20540,17 +21019,17 @@
 Lasclay.com</t>
         </is>
       </c>
-      <c r="L290" s="5" t="n"/>
-      <c r="M290" s="5" t="n"/>
-      <c r="N290" s="6" t="n"/>
+      <c r="L296" s="5" t="n"/>
+      <c r="M296" s="5" t="n"/>
+      <c r="N296" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N290"/>
+  <autoFilter ref="A1:N296"/>
   <dataValidations count="2">
-    <dataValidation sqref="N2:N290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N296" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"à réécrire au complet,à corriger,bon,ne pas envoyer"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I296" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"tu,vous,—"</formula1>
     </dataValidation>
   </dataValidations>

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>L'asclépiade à Dragons' Den le 17 septembre</t>
+          <t>L'asclépiade à Dragons' Den!</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vos lecteurs aimeraient voir comment une gousse devient un manteau.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2307,7 +2307,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2376,7 +2376,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2445,7 +2445,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2514,7 +2514,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2583,7 +2583,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2652,7 +2652,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2721,7 +2721,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2790,7 +2790,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2859,7 +2859,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2928,7 +2928,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2997,7 +2997,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3066,7 +3066,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3135,7 +3135,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3204,7 +3204,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3273,7 +3273,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3342,7 +3342,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3407,11 +3407,11 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3479,7 +3479,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet : huit ans après Saint-Tite, il reste quelque chose de cette promesse-là, et ça se raconte.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3548,7 +3548,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3617,7 +3617,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3686,7 +3686,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3755,7 +3755,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3824,7 +3824,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3893,7 +3893,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3962,7 +3962,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4031,7 +4031,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4100,7 +4100,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4169,7 +4169,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4238,7 +4238,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4307,7 +4307,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4376,7 +4376,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4445,7 +4445,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4514,7 +4514,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4583,7 +4583,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4648,11 +4648,11 @@
           <t>Bonjour Marianne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4721,7 +4721,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4790,7 +4790,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4859,7 +4859,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4928,7 +4928,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4997,7 +4997,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5066,7 +5066,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5135,7 +5135,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5204,7 +5204,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part parce que vos lecteurs ont vu la promesse de l'asclépiade de plus près que n'importe qui. Qui sait, peut-être vous inspirer un sujet sur ce que la plante est devenue depuis. Je peux parler des volumes, de la récolte, et de ce qui reste à régler.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5273,7 +5273,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5342,7 +5342,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5411,7 +5411,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5480,7 +5480,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5549,7 +5549,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5618,7 +5618,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5687,7 +5687,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5756,7 +5756,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5825,7 +5825,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5894,7 +5894,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5963,7 +5963,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6032,7 +6032,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6101,7 +6101,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6170,7 +6170,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6239,7 +6239,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6308,7 +6308,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6377,7 +6377,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6446,7 +6446,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6515,7 +6515,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6584,7 +6584,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6653,7 +6653,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6718,11 +6718,11 @@
           <t>Bonjour Scott,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6791,7 +6791,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6860,7 +6860,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6925,11 +6925,11 @@
           <t>Bonjour Karine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6998,7 +6998,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7067,7 +7067,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7136,7 +7136,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7205,7 +7205,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7274,7 +7274,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7343,7 +7343,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7412,7 +7412,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7481,7 +7481,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7550,7 +7550,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7615,11 +7615,11 @@
           <t>Bonjour Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7688,7 +7688,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7757,7 +7757,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7826,7 +7826,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7895,7 +7895,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7964,7 +7964,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8033,7 +8033,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8102,7 +8102,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8171,7 +8171,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8240,7 +8240,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8309,7 +8309,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8378,7 +8378,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8447,7 +8447,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8516,7 +8516,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8585,7 +8585,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8654,7 +8654,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8723,7 +8723,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8792,7 +8792,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8861,7 +8861,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8926,12 +8926,12 @@
           <t>Bonjour Chloé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9000,7 +9000,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9069,7 +9069,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9138,7 +9138,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9207,7 +9207,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9272,12 +9272,12 @@
           <t>Bonjour Jacinthe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9346,7 +9346,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9411,11 +9411,11 @@
           <t>Bonjour Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9480,11 +9480,11 @@
           <t>Bonjour Yves,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9553,7 +9553,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9622,7 +9622,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9691,7 +9691,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9760,7 +9760,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9829,7 +9829,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9898,7 +9898,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9967,7 +9967,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10036,7 +10036,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10101,11 +10101,11 @@
           <t>Bonjour Carole,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10174,7 +10174,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10243,7 +10243,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10312,7 +10312,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10381,7 +10381,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10450,7 +10450,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10519,7 +10519,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10584,11 +10584,11 @@
           <t>Bonjour Michel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10657,7 +10657,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10726,7 +10726,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10795,7 +10795,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10860,12 +10860,12 @@
           <t>Bonjour Anick,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10934,7 +10934,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11003,7 +11003,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11068,11 +11068,11 @@
           <t>Bonjour Julia,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11141,7 +11141,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11210,7 +11210,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11279,7 +11279,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11348,7 +11348,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11417,7 +11417,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11486,7 +11486,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11555,7 +11555,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11624,7 +11624,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11693,7 +11693,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11762,7 +11762,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11831,7 +11831,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11900,7 +11900,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11969,7 +11969,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12038,7 +12038,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12107,7 +12107,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12176,7 +12176,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12245,7 +12245,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12314,7 +12314,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12383,7 +12383,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12452,7 +12452,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12521,7 +12521,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12590,7 +12590,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12655,11 +12655,11 @@
           <t>Bonjour Thomas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12728,7 +12728,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12797,7 +12797,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12866,7 +12866,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12935,7 +12935,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13004,7 +13004,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13073,7 +13073,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13142,7 +13142,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13211,7 +13211,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13280,7 +13280,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13349,7 +13349,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13418,7 +13418,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13487,7 +13487,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13556,7 +13556,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13625,7 +13625,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13694,7 +13694,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13763,7 +13763,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13832,7 +13832,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13901,7 +13901,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13970,7 +13970,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14039,7 +14039,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14108,7 +14108,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14177,7 +14177,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14246,7 +14246,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14315,7 +14315,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14384,7 +14384,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14453,7 +14453,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14522,7 +14522,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14591,7 +14591,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14660,7 +14660,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14729,7 +14729,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14798,7 +14798,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14867,7 +14867,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14932,11 +14932,11 @@
           <t>Bonjour Timothy,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15005,7 +15005,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15074,7 +15074,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15143,7 +15143,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15208,11 +15208,11 @@
           <t>Bonjour Isaac,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15281,7 +15281,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15350,7 +15350,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15419,7 +15419,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15488,7 +15488,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15557,7 +15557,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15626,7 +15626,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15695,7 +15695,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15764,7 +15764,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15833,7 +15833,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15898,11 +15898,11 @@
           <t>Bonjour Louis-Philippe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après la faillite d'octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
+Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15971,7 +15971,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière de vos yeux.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16040,7 +16040,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16109,7 +16109,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16178,7 +16178,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16247,7 +16247,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16316,7 +16316,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16385,7 +16385,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16454,7 +16454,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16523,7 +16523,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16592,7 +16592,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16661,7 +16661,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16730,7 +16730,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16795,12 +16795,12 @@
           <t>Bonjour Paule,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16869,7 +16869,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16938,7 +16938,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -17007,7 +17007,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -17076,7 +17076,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -17145,7 +17145,7 @@
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -17212,7 +17212,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 I'm writing to the wire first because if this is worth two paragraphs, it's worth them in every paper in the country: a Quebec company insulating winter coats with the only plant monarch caterpillars can eat is going on national television Thursday.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17285,7 +17285,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 The business story: we built our own processing because no subcontractor would touch the fibre, changed our manufacturing model last year to survive, and are now pitching on national television.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17358,7 +17358,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17431,7 +17431,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17504,7 +17504,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17577,7 +17577,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here, Thursday's national broadcast is a local story first.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17650,7 +17650,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields. The coat on the shelf begins as a pod in a row of weeds somebody decided not to spray.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17698,7 +17698,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain. The Quebec filière collapsed on October 11, 2017 when the group that had reserved 90 per cent of the crop went bankrupt (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), which is the context for anything written about milkweed insulation today.</t>
+          <t>You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain. The Quebec filière collapsed [on October 11, 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) when the group that had reserved 90 per cent of the crop went bankrupt, which is the context for anything written about milkweed insulation today.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -17721,9 +17721,9 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain. The Quebec filière collapsed on October 11, 2017 when the group that had reserved 90 per cent of the crop went bankrupt (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), which is the context for anything written about milkweed insulation today.
+You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain. The Quebec filière collapsed [on October 11, 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) when the group that had reserved 90 per cent of the crop went bankrupt, which is the context for anything written about milkweed insulation today.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17796,7 +17796,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17869,7 +17869,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments. That last step is where the earlier attempts stopped.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -17942,7 +17942,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Plant-based insulation is one of the few places where outerwear can actually leave animal and petroleum fibres behind, and milkweed is the rare one that also feeds a threatened pollinator.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18015,7 +18015,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18088,7 +18088,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18161,7 +18161,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18234,7 +18234,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18307,7 +18307,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18380,7 +18380,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18453,7 +18453,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18526,7 +18526,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18599,7 +18599,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 A $300 winter coat insulated with a farm weed instead of down or polyester. The consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18672,7 +18672,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18745,7 +18745,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18818,7 +18818,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18891,7 +18891,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -18964,7 +18964,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19037,7 +19037,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments, which is the part nobody had managed to hold.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19110,7 +19110,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 The business angle from the Atlantic side: we built our own processing because no subcontractor would touch the fibre, and we are about to pitch it on national television. Atlantic Canada has the same problem we had, a raw material with no processing chain.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19183,7 +19183,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19256,7 +19256,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19329,7 +19329,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19402,7 +19402,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19475,7 +19475,7 @@
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
 The farm side of it: milkweed is a weed most growers spray, and a Quebec cooperative of 125 producers lost its only buyer overnight in 2017. We still buy the harvest. That question, whether anyone is waiting at the end of the field, is not specific to Quebec.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19523,7 +19523,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. It stopped on October 11, 2017, when the group that had reserved 90 per cent of the Quebec crop went bankrupt and 125 growers lost their buyer overnight (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). We still buy the harvest, and that is the part that decides whether anyone plants it again.</t>
+          <t>The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. It stopped on October 11, 2017, when the group that had reserved 90 per cent of the Quebec crop went bankrupt and 125 growers lost their buyer overnight[, as Radio-Canada reported at the time](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). We still buy the harvest, and that is the part that decides whether anyone plants it again.</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -19546,9 +19546,9 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
-The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. It stopped on October 11, 2017, when the group that had reserved 90 per cent of the Quebec crop went bankrupt and 125 growers lost their buyer overnight (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). We still buy the harvest, and that is the part that decides whether anyone plants it again.
+The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. It stopped on October 11, 2017, when the group that had reserved 90 per cent of the Quebec crop went bankrupt and 125 growers lost their buyer overnight[, as Radio-Canada reported at the time](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). We still buy the harvest, and that is the part that decides whether anyone plants it again.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
-If you'd like to cover it, or a colleague might, our media kit is here, with images from the Dragons' Den floor and of the company: https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
 I'm hoping this visibility moves sales, which more broadly is very good news for the Quebec milkweed growers we keep buying from, and for the threatened monarchs that keep breeding in their fields.
 Happy to answer any questions, and available for an interview this week.
 Warmly,
@@ -19614,11 +19614,11 @@
           <t>Bonjour Johanne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -19684,11 +19684,11 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -19754,11 +19754,11 @@
           <t>Bonjour France,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -19824,11 +19824,11 @@
           <t>Bonjour Gilbert,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -19894,11 +19894,11 @@
           <t>Bonjour Carine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -19964,11 +19964,11 @@
           <t>Bonjour Maxime,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20034,11 +20034,11 @@
           <t>Bonjour Marie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20104,11 +20104,11 @@
           <t>Bonjour Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20174,11 +20174,11 @@
           <t>Bonjour Marc-Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20244,11 +20244,11 @@
           <t>Bonjour Benoit,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
+Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20317,7 +20317,7 @@
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20386,7 +20386,7 @@
 Notre atelier est à Québec, et c'est là que la soie d'asclépiade devient de l'isolant.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20455,7 +20455,7 @@
 Je vous écris parce que Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive de l'asclépiade pour nous depuis nos tout débuts, et qu'il en cultive encore. Je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20521,11 +20521,11 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite le 11 octobre 2017 (https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, la MRC de Mékinac a fait pencher la relance (https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20591,10 +20591,10 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées le 11 octobre 2017 avec une dette de plus de 1,4 M$ (https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/). L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
+Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20663,7 +20663,7 @@
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20732,7 +20732,7 @@
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20801,7 +20801,7 @@
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20870,7 +20870,7 @@
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -20939,7 +20939,7 @@
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,
@@ -21008,7 +21008,7 @@
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
-Si ça vous intéresse de couvrir (ou un.e collègue?), notre média kit est ici, avec les images de notre passage à Dragons' Den et de l'entreprise : https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr
+Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.
 Chaleureusement,

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -2303,6 +2303,7 @@
           <t>Bonjour Zoé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2372,6 +2373,7 @@
           <t>Bonjour Victoria,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2441,6 +2443,7 @@
           <t>Bonjour Marie-Émélie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2510,6 +2513,7 @@
           <t>Bonjour Normand,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2579,6 +2583,7 @@
           <t>Bonjour Louise,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2648,6 +2653,7 @@
           <t>Bonjour Francois,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2717,6 +2723,7 @@
           <t>Bonjour Ariane,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2786,6 +2793,7 @@
           <t>Bonjour Gilbert,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2855,6 +2863,7 @@
           <t>Bonjour Papa Moussa,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2924,6 +2933,7 @@
           <t>Bonjour Victor,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2993,6 +3003,7 @@
           <t>Bonjour Eric,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3062,6 +3073,7 @@
           <t>Bonjour Tristan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3131,6 +3143,7 @@
           <t>Bonjour Jean-Marc,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3200,6 +3213,7 @@
           <t>Bonjour Simon,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3269,6 +3283,7 @@
           <t>Bonjour Maxime,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3338,6 +3353,7 @@
           <t>Bonjour Aurélia,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3407,6 +3423,7 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3475,10 +3492,12 @@
         <is>
           <t>Bonjour Gabriel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-L'asclépiade a été une histoire mauricienne avant d'être la nôtre : l'usine de Saint-Tite achetait 90 % des récoltes du Québec. On a démarré après la chute de cette filière, et six ans plus tard on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec.
-Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet : huit ans après Saint-Tite, il reste quelque chose de cette promesse-là, et ça se raconte.
+Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
+Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
+Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet : neuf ans après la faillite, il reste quelque chose de cette promesse-là, et ça se raconte.
 Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
@@ -3544,6 +3563,7 @@
           <t>Bonjour Anaïs,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3613,6 +3633,7 @@
           <t>Bonjour Simon,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3682,6 +3703,7 @@
           <t>Bonjour Karl-Ivann,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3751,6 +3773,7 @@
           <t>Bonjour André,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3820,6 +3843,7 @@
           <t>Bonjour Myriam,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3889,6 +3913,7 @@
           <t>Bonjour Étienne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3958,6 +3983,7 @@
           <t>Bonjour Johanne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4027,6 +4053,7 @@
           <t>Bonjour Jean,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4096,6 +4123,7 @@
           <t>Bonjour Cécile,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4165,6 +4193,7 @@
           <t>Bonjour Marieke,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4234,6 +4263,7 @@
           <t>Bonjour Maude,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4303,6 +4333,7 @@
           <t>Bonjour Pauline,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4372,6 +4403,7 @@
           <t>Bonjour Bernard,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4441,6 +4473,7 @@
           <t>Bonjour Leïla,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4510,6 +4543,7 @@
           <t>Bonjour Kodjo Edjinam Nulagnon,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4579,6 +4613,7 @@
           <t>Bonjour Annie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4648,6 +4683,7 @@
           <t>Bonjour Marianne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4717,6 +4753,7 @@
           <t>Bonjour Sophie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4786,6 +4823,7 @@
           <t>Bonjour Alain,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4855,6 +4893,7 @@
           <t>Bonjour Mikaël,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4924,6 +4963,7 @@
           <t>Bonjour Jean-Luc,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4993,6 +5033,7 @@
           <t>Bonjour Jean-Francois,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5062,6 +5103,7 @@
           <t>Bonjour Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5131,6 +5173,7 @@
           <t>Bonjour Annie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5199,8 +5242,8 @@
         <is>
           <t>Bonjour Réjean,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment industriel au Québec. L'usine achetait 90 % des récoltes de la province avant que la filière se casse le 11 octobre 2017.
-On a démarré après. Six ans plus tard, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec.
+Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment industriel au Québec. Le groupe Protec-Style, qui exploitait l'usine sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), et c'est [l'appui de la MRC qui a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922) six semaines plus tard. On a démarré après. Neuf ans plus tard, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part parce que vos lecteurs ont vu la promesse de l'asclépiade de plus près que n'importe qui. Qui sait, peut-être vous inspirer un sujet sur ce que la plante est devenue depuis. Je peux parler des volumes, de la récolte, et de ce qui reste à régler.
@@ -5269,6 +5312,7 @@
           <t>Bonjour Charles,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5338,6 +5382,7 @@
           <t>Bonjour Clara,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5407,6 +5452,7 @@
           <t>Bonjour Valérian,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5476,6 +5522,7 @@
           <t>Bonjour Lili,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5545,6 +5592,7 @@
           <t>Bonjour Nicolas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5614,6 +5662,7 @@
           <t>Bonjour Nicolas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5683,6 +5732,7 @@
           <t>Bonjour Véronique,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5752,6 +5802,7 @@
           <t>Bonjour Lila,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5821,6 +5872,7 @@
           <t>Bonjour Olivier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5890,6 +5942,7 @@
           <t>Bonjour Emmanuelle,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5959,6 +6012,7 @@
           <t>Bonjour Jean-Benoît,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6028,6 +6082,7 @@
           <t>Bonjour Yves,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6097,6 +6152,7 @@
           <t>Bonjour Josée,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6166,6 +6222,7 @@
           <t>Bonjour Yannick,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6235,6 +6292,7 @@
           <t>Bonjour Félix,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6304,6 +6362,7 @@
           <t>Bonjour Marie-Eve,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6373,6 +6432,7 @@
           <t>Bonjour Marie-Hélène,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6442,6 +6502,7 @@
           <t>Bonjour Jean-Hugues,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6511,6 +6572,7 @@
           <t>Bonjour Martin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6580,6 +6642,7 @@
           <t>Bonjour Sylvain,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6649,6 +6712,7 @@
           <t>Bonjour Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6718,6 +6782,7 @@
           <t>Bonjour Scott,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6787,6 +6852,7 @@
           <t>Bonjour Michèle,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6856,6 +6922,7 @@
           <t>Bonjour Stephane,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6925,6 +6992,7 @@
           <t>Bonjour Karine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6994,6 +7062,7 @@
           <t>Bonjour Jean-Francois,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7063,6 +7132,7 @@
           <t>Bonjour Shahram,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7132,6 +7202,7 @@
           <t>Bonjour Malika,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7201,6 +7272,7 @@
           <t>Bonjour Yahia,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7270,6 +7342,7 @@
           <t>Bonjour MARC-OLIVIER,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7339,6 +7412,7 @@
           <t>Bonjour Maïté,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7408,6 +7482,7 @@
           <t>Bonjour André,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7477,6 +7552,7 @@
           <t>Bonjour Didier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7546,6 +7622,7 @@
           <t>Bonjour Sophie-Andrée,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7615,6 +7692,7 @@
           <t>Bonjour Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7684,6 +7762,7 @@
           <t>Bonjour Gilles,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7753,6 +7832,7 @@
           <t>Bonjour Daphné,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7822,6 +7902,7 @@
           <t>Bonjour Godefroy Macaire,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7891,6 +7972,7 @@
           <t>Bonjour Sara,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7960,6 +8042,7 @@
           <t>Bonjour Sarah,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8029,6 +8112,7 @@
           <t>Bonjour Éric-Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8098,6 +8182,7 @@
           <t>Bonjour Marine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8167,6 +8252,7 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8236,6 +8322,7 @@
           <t>Bonjour Laurence,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8305,6 +8392,7 @@
           <t>Bonjour Amélie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8374,6 +8462,7 @@
           <t>Bonjour Dominique,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8443,6 +8532,7 @@
           <t>Bonjour Quentin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8512,6 +8602,7 @@
           <t>Bonjour Ève,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8581,6 +8672,7 @@
           <t>Bonjour Michel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8650,6 +8742,7 @@
           <t>Bonjour Marie-Eve,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8719,6 +8812,7 @@
           <t>Bonjour Raymond,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8788,6 +8882,7 @@
           <t>Bonjour Marie-Pier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8857,6 +8952,7 @@
           <t>Bonjour Marie-Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8926,6 +9022,7 @@
           <t>Bonjour Chloé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
@@ -8996,6 +9093,7 @@
           <t>Bonjour Charlotte,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9065,6 +9163,7 @@
           <t>Bonjour Annie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9134,6 +9233,7 @@
           <t>Bonjour Ahmed,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9203,6 +9303,7 @@
           <t>Bonjour Tania,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9272,6 +9373,7 @@
           <t>Bonjour Jacinthe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
@@ -9342,6 +9444,7 @@
           <t>Bonjour Bruno,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9411,6 +9514,7 @@
           <t>Bonjour Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9480,6 +9584,7 @@
           <t>Bonjour Yves,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9549,6 +9654,7 @@
           <t>Bonjour Anne Marie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9618,6 +9724,7 @@
           <t>Bonjour Stéphanie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9687,6 +9794,7 @@
           <t>Bonjour Philippe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9756,6 +9864,7 @@
           <t>Bonjour Gildas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9825,6 +9934,7 @@
           <t>Bonjour Louis-Xavier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9894,6 +10004,7 @@
           <t>Bonjour Anne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9963,6 +10074,7 @@
           <t>Bonjour Karianne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10032,6 +10144,7 @@
           <t>Bonjour Geneviève,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10101,6 +10214,7 @@
           <t>Bonjour Carole,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10170,6 +10284,7 @@
           <t>Bonjour Boris,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10239,6 +10354,7 @@
           <t>Bonjour Philippe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10308,6 +10424,7 @@
           <t>Bonjour Gwen,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10377,6 +10494,7 @@
           <t>Bonjour Mathieu-Robert,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10446,6 +10564,7 @@
           <t>Bonjour Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis la faillite du 11 octobre 2017 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10515,6 +10634,7 @@
           <t>Bonjour Katherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10584,6 +10704,7 @@
           <t>Bonjour Michel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10653,6 +10774,7 @@
           <t>Bonjour Martin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10722,6 +10844,7 @@
           <t>Bonjour Yanick,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10791,6 +10914,7 @@
           <t>Bonjour Jonathan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10860,6 +10984,7 @@
           <t>Bonjour Anick,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
@@ -10930,6 +11055,7 @@
           <t>Bonjour Félix-Antoine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10999,6 +11125,7 @@
           <t>Bonjour Karim,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11068,6 +11195,7 @@
           <t>Bonjour Julia,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11137,6 +11265,7 @@
           <t>Bonjour Karine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11206,6 +11335,7 @@
           <t>Bonjour Audrey,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11275,6 +11405,7 @@
           <t>Bonjour Luc,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11344,6 +11475,7 @@
           <t>Bonjour Mario,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11413,6 +11545,7 @@
           <t>Bonjour Bernard,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11482,6 +11615,7 @@
           <t>Bonjour Pierre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11551,6 +11685,7 @@
           <t>Bonjour Laurence,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11620,6 +11755,7 @@
           <t>Bonjour Nathaniel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11689,6 +11825,7 @@
           <t>Bonjour Marie-France,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11758,6 +11895,7 @@
           <t>Bonjour Diane,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11827,6 +11965,7 @@
           <t>Bonjour Julien,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11896,6 +12035,7 @@
           <t>Bonjour Rudy,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11965,6 +12105,7 @@
           <t>Bonjour Denis-Martin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12034,6 +12175,7 @@
           <t>Bonjour Loubna Majda,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12103,6 +12245,7 @@
           <t>Bonjour Sarah,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12172,6 +12315,7 @@
           <t>Bonjour Kathleen,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12241,6 +12385,7 @@
           <t>Bonjour Oumou,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12310,6 +12455,7 @@
           <t>Bonjour Agnès,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12379,6 +12525,7 @@
           <t>Bonjour Marcelin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12448,6 +12595,7 @@
           <t>Bonjour Alain,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12517,6 +12665,7 @@
           <t>Bonjour Ivanoh,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12586,6 +12735,7 @@
           <t>Bonjour Claude,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12655,6 +12805,7 @@
           <t>Bonjour Thomas,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12724,6 +12875,7 @@
           <t>Bonjour Claude,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12793,6 +12945,7 @@
           <t>Bonjour Martine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12862,6 +13015,7 @@
           <t>Bonjour Marie-Claude,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12931,6 +13085,7 @@
           <t>Bonjour Jean-René,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13000,6 +13155,7 @@
           <t>Bonjour Richard,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13069,6 +13225,7 @@
           <t>Bonjour Stéphanie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13138,6 +13295,7 @@
           <t>Bonjour Maxim,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13207,6 +13365,7 @@
           <t>Bonjour Ronald,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13276,6 +13435,7 @@
           <t>Bonjour Stéphane,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13345,6 +13505,7 @@
           <t>Bonjour Zacharie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13414,6 +13575,7 @@
           <t>Bonjour Isabelle,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13483,6 +13645,7 @@
           <t>Bonjour Chantal,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13552,6 +13715,7 @@
           <t>Bonjour Matthieu,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13618,16 +13782,7 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>Bonjour Francis,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
-Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
-J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
-Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
+          <t>NE PAS ENVOYER, doublon de la liste chaude. Le message écrit à la main a préséance.</t>
         </is>
       </c>
       <c r="L191" s="5" t="n"/>
@@ -13690,6 +13845,7 @@
           <t>Bonjour ANGELO,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13759,6 +13915,7 @@
           <t>Bonjour Andréanne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13828,6 +13985,7 @@
           <t>Bonjour Hugo,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13897,6 +14055,7 @@
           <t>Bonjour Philémon,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13966,6 +14125,7 @@
           <t>Bonjour Henri,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14032,16 +14192,7 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>Bonjour Annie,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
-Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
-Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
-Si ça vous intéresse de couvrir (ou un.e collègue?), [notre média kit est ici](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), avec les images de notre passage à Dragons' Den et de l'entreprise.
-J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
-Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
+          <t>NE PAS ENVOYER, doublon de la liste chaude. Le message écrit à la main a préséance.</t>
         </is>
       </c>
       <c r="L197" s="5" t="n"/>
@@ -14104,6 +14255,7 @@
           <t>Bonjour Joannie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14173,6 +14325,7 @@
           <t>Bonjour Angie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14242,6 +14395,7 @@
           <t>Bonjour Camille,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14311,6 +14465,7 @@
           <t>Bonjour Claudia,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14380,6 +14535,7 @@
           <t>Bonjour Étienne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14449,6 +14605,7 @@
           <t>Bonjour Louise,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14518,6 +14675,7 @@
           <t>Bonjour Guillaume,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14587,6 +14745,7 @@
           <t>Bonjour Roxane,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14656,6 +14815,7 @@
           <t>Bonjour Ève,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14725,6 +14885,7 @@
           <t>Bonjour Sophie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14794,6 +14955,7 @@
           <t>Bonjour Colin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14863,6 +15025,7 @@
           <t>Bonjour Isabelle,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14932,6 +15095,7 @@
           <t>Bonjour Timothy,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15001,6 +15165,7 @@
           <t>Bonjour Rachid,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15070,6 +15235,7 @@
           <t>Bonjour Richard,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15139,6 +15305,7 @@
           <t>Bonjour MELISSA,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15208,6 +15375,7 @@
           <t>Bonjour Isaac,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15277,6 +15445,7 @@
           <t>Bonjour Frédéric,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15346,6 +15515,7 @@
           <t>Bonjour Nathalie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15415,6 +15585,7 @@
           <t>Bonjour Francis,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15484,6 +15655,7 @@
           <t>Bonjour Raymonde,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15553,6 +15725,7 @@
           <t>Bonjour Richard,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15622,6 +15795,7 @@
           <t>Bonjour Pascale,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15691,6 +15865,7 @@
           <t>Bonjour Marc Sony,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15760,6 +15935,7 @@
           <t>Bonjour Marie-Paul,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15829,6 +16005,7 @@
           <t>Bonjour Emmalie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15898,6 +16075,7 @@
           <t>Bonjour Louis-Philippe,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade se cultive chez vous depuis la première vague de 2013, celle de la Coopérative Monark et de ses 125 producteurs. Plusieurs de ceux qui ont tenu bon après [la faillite d'octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) nous vendent encore leur récolte.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15967,6 +16145,7 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16036,6 +16215,7 @@
           <t>Bonjour Olivier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16105,6 +16285,7 @@
           <t>Bonjour Jacques,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16174,6 +16355,7 @@
           <t>Bonjour Alexandre,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16243,6 +16425,7 @@
           <t>Bonjour Chloé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16312,6 +16495,7 @@
           <t>Bonjour Kimberley,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16381,6 +16565,7 @@
           <t>Bonjour William,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme à Québec.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16450,6 +16635,7 @@
           <t>Bonjour Katia,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16519,6 +16705,7 @@
           <t>Bonjour Martin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16588,6 +16775,7 @@
           <t>Bonjour Marie-Christine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16657,6 +16845,7 @@
           <t>Bonjour Pierre-Luc,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16726,6 +16915,7 @@
           <t>Bonjour David,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16795,6 +16985,7 @@
           <t>Bonjour Paule,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
@@ -16865,6 +17056,7 @@
           <t>Bonjour Alexandra,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16934,6 +17126,7 @@
           <t>Bonjour Raymond,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17003,6 +17196,7 @@
           <t>Bonjour Paul Émile,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17072,6 +17266,7 @@
           <t>Bonjour Augustin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17141,6 +17336,7 @@
           <t>Bonjour Ivan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Ce jeudi 17 septembre, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17210,6 +17406,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 I'm writing to the wire first because if this is worth two paragraphs, it's worth them in every paper in the country: a Quebec company insulating winter coats with the only plant monarch caterpillars can eat is going on national television Thursday.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17283,6 +17480,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 The business story: we built our own processing because no subcontractor would touch the fibre, changed our manufacturing model last year to survive, and are now pitching on national television.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17356,6 +17554,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Quebec company built its own processing because no subcontractor would touch the fibre, changed its manufacturing model last year to survive, and is now pitching on national television. Whatever happens in the episode, the fibre and the farms behind it are real.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17429,6 +17628,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17502,6 +17702,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars eat.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17575,6 +17776,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 We're a Quebec City company, the milkweed is grown by Quebec farmers, and the insulation is made here, Thursday's national broadcast is a local story first.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17648,6 +17850,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 We're a Canadian direct-to-consumer brand about to get national television exposure, with a supply chain that starts in Quebec fields. The coat on the shelf begins as a pod in a row of weeds somebody decided not to spray.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17721,6 +17924,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 You covered Vegeto's milkweed insulation last February. We're the other end of that same Quebec filière: we buy the harvest, process the floss into insulation ourselves, and sell finished garments. As far as we know, nobody else holds the whole chain. The Quebec filière collapsed [on October 11, 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark) when the group that had reserved 90 per cent of the crop went bankrupt, which is the context for anything written about milkweed insulation today.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17794,6 +17998,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17867,6 +18072,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal, and a Quebec filière has been trying to industrialise it since 2013. We process it ourselves and sell finished garments. That last step is where the earlier attempts stopped.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -17940,6 +18146,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Plant-based insulation is one of the few places where outerwear can actually leave animal and petroleum fibres behind, and milkweed is the rare one that also feeds a threatened pollinator.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18013,6 +18220,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18086,6 +18294,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18159,6 +18368,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18232,6 +18442,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18305,6 +18516,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18378,6 +18590,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18451,6 +18664,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18524,6 +18738,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A Canadian company goes on Dragons' Den this Thursday with a winter coat insulated by a weed most farmers spray, and that same weed is the only thing monarch caterpillars can eat. We grow it, we process the floss into insulation ourselves in Quebec City, and we sell the finished garments across the country.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18597,6 +18812,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 A $300 winter coat insulated with a farm weed instead of down or polyester. The consumer question is whether it actually keeps you warm, and that is a fair thing to test on air.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18670,6 +18886,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18743,6 +18960,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18816,6 +19034,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18889,6 +19108,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -18962,6 +19182,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers can watch it Thursday night. The milkweed is grown by Quebec farmers and the floss is processed into insulation in Quebec City. Final assembly of the garments happens offshore, which is what put the coat near $300 instead of the $1,000 the earlier attempts asked.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19035,6 +19256,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Milkweed floss is a hollow, naturally water-repellent fibre that behaves like down without an animal. A Quebec filière has been trying to industrialise it since 2013; we process it ourselves and sell finished garments, which is the part nobody had managed to hold.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19108,6 +19330,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 The business angle from the Atlantic side: we built our own processing because no subcontractor would touch the fibre, and we are about to pitch it on national television. Atlantic Canada has the same problem we had, a raw material with no processing chain.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19181,6 +19404,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19254,6 +19478,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19327,6 +19552,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19400,6 +19626,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 Your readers buy winter coats to work in, not to walk to the car. Ours is insulated with a plant fibre instead of down or polyester, and I would rather have it judged by people who actually need it to hold at forty below than by anyone in a city. I'll send one to a reporter who wants to try it and say publicly what they found, good or bad.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19473,6 +19700,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 The farm side of it: milkweed is a weed most growers spray, and a Quebec cooperative of 125 producers lost its only buyer overnight in 2017. We still buy the harvest. That question, whether anyone is waiting at the end of the field, is not specific to Quebec.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19546,6 +19774,7 @@
           <t>Hello,
 My name is Gabriel Gouveia, founder of Lasclay. We insulate winter clothing with a weed called milkweed, which we grow to help save an emblematic, threatened pollinator: the monarch butterfly.
 Its pods are filled with a hollow floss, very light and naturally water-repellent. We turn it into insulation in Quebec City and put it into coats, mitts, toques and cooler bags sold across Canada and the United States.
+Milkweed is not an imported plant: it is a [weed native to eastern Canada](https://lasclay.com/en-us/pages/milkweed-plant-fiber), which is exactly why [the monarch depends on it](https://lasclay.com/en-us/pages/monarch-butterfly). It also has a longer history than we do. We wrote down what we found: [American silk in New France](https://lasclay.com/en-us/blogs/journal/soie-amerique-nouvelle-france), [the children who picked it for Second World War life jackets](https://lasclay.com/en-us/blogs/journal/asclepiade-seconde-guerre-mondiale), and [the story of the Quebec industry](https://lasclay.com/en-us/blogs/journal/histoire-industrie-asclepiade-quebec).
 The farm side: milkweed is a weed most growers spray, and a Quebec filière has been trying since 2013 to make it pay at the field gate. It stopped on October 11, 2017, when the group that had reserved 90 per cent of the Quebec crop went bankrupt and 125 growers lost their buyer overnight[, as Radio-Canada reported at the time](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). We still buy the harvest, and that is the part that decides whether anyone plants it again.
 This Thursday, September 17, Lasclay is in the first episode of season 21 of Dragons' Den, on CBC and CBC Gem at 8 p.m. (8:30 NT).
 If you'd like to cover it, or a colleague might, [our media kit is here](https://drive.google.com/drive/folders/1pyCUbfHYQhpXXl4FoCC2RCFXKRvGS5Zr), with images from the Dragons' Den floor and of the company.
@@ -19614,6 +19843,7 @@
           <t>Bonjour Johanne,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -19684,6 +19914,7 @@
           <t>Bonjour Catherine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -19754,6 +19985,7 @@
           <t>Bonjour France,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -19824,6 +20056,7 @@
           <t>Bonjour Gilbert,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -19894,6 +20127,7 @@
           <t>Bonjour Carine,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -19964,6 +20198,7 @@
           <t>Bonjour Maxime,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -20034,6 +20269,7 @@
           <t>Bonjour Marie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -20104,6 +20340,7 @@
           <t>Bonjour Julie,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -20174,6 +20411,7 @@
           <t>Bonjour Marc-Yvan,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -20244,6 +20482,7 @@
           <t>Bonjour Benoit,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade est une histoire agricole avec une date de rupture. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3 et avait réservé 90 % de la récolte québécoise, a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark). Les 125 producteurs de la Coopérative Monark se sont retrouvés sans acheteur, et la question n'a pas changé depuis : y a-t-il quelqu'un au bout du champ.
 Nous, on achète encore. Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive pour nous depuis nos tout débuts, et je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -20314,6 +20553,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20383,6 +20623,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Notre atelier est à Québec, et c'est là que la soie d'asclépiade devient de l'isolant.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20452,6 +20693,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que Sabin Tremblay, à L'Ascension-de-Notre-Seigneur, cultive de l'asclépiade pour nous depuis nos tout débuts, et qu'il en cultive encore. Je vais l'aider à récolter le 4 octobre. S'il y a un reportage à faire, il est là autant qu'ici.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20521,6 +20763,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que l'asclépiade a commencé chez vous, à Saint-Tite et dans Mékinac. Le groupe Protec-Style, qui exploitait l'usine de Saint-Tite sous le nom d'Encore 3, avait réservé 90 % de la récolte québécoise quand il a fait faillite [le 11 octobre 2017](https://ici.radio-canada.ca/nouvelle/1061543/asclepiade-soyer-producteurs-industries-encore3-faillite-monark), emportant Saint-Tite et son atelier de Granby. Les 125 producteurs de la Coopérative Monark ont pris le choc. Six semaines plus tard, [la MRC de Mékinac a fait pencher la relance](https://lenouvelliste.ca/affaires/asclepiade-les-activites-reprennent-a-lusine-de-saint-tite-9a7c0d08d77c81c7ab22fdfc8e47a922).
 Neuf ans après, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec. Ce jeudi, c'est cette plante-là que je vais défendre à la télévision nationale.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
@@ -20591,6 +20834,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que la transformation de la fibre se faisait à Granby, rue Bernard. L'atelier appartenait au groupe Protec-Style, qui exploitait aussi l'usine de Saint-Tite, et les deux sont tombées [le 11 octobre 2017](https://www.lhebdodustmaurice.com/actualite/protec-style-en-faillite/) avec une dette de plus de 1,4 M$. L'Estrie compte encore des producteurs d'asclépiade, et on continue d'acheter de la fibre québécoise.
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20660,6 +20904,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20729,6 +20974,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20798,6 +21044,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20867,6 +21114,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -20936,6 +21184,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
@@ -21005,6 +21254,7 @@
           <t>Bonjour,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
 Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+L'asclépiade n'est pas une plante importée : c'est une [mauvaise herbe indigène](https://lasclay.com/pages/milkweed-asclepiade) qui pousse ici depuis toujours, et c'est pour ça que [le monarque en dépend](https://lasclay.com/pages/monarch-butterfly). Elle a aussi une histoire plus longue que la nôtre. On a écrit ce qu'on en a trouvé : [la soie d'Amérique en Nouvelle-France](https://lasclay.com/blogs/journal/soie-amerique-nouvelle-france), [les enfants qui la récoltaient pour les gilets de sauvetage de la Seconde Guerre mondiale](https://lasclay.com/blogs/journal/asclepiade-seconde-guerre-mondiale), et [l'histoire de l'industrie québécoise](https://lasclay.com/blogs/journal/histoire-industrie-asclepiade-quebec).
 Je vous écris parce que c'est d'abord une histoire d'affaires : bâtir ses propres procédés faute de sous-traitant prêt à toucher à la fibre, puis changer de modèle manufacturier l'an dernier pour tenir, et se retrouver à pitcher à la télévision nationale. La vidéo sur le changement de modèle est ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU
 Ce jeudi 17 septembre, je présente Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem, à 20 h.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue d'ici jeudi, ou le vendredi 18 au matin.
